--- a/AAII.xlsx
+++ b/AAII.xlsx
@@ -9,14 +9,14 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="W3xo9H51ZcXKsz3Sn+q68L0g3NGO3Ff6guFUuj7349s="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="wDXvabttsKun171Rni81VIHwM6VhsjY4ECO6QmsPaMk="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="100">
   <si>
     <t>Company</t>
   </si>
@@ -78,7 +78,7 @@
     <t>CTRM</t>
   </si>
   <si>
-    <t>News Archive for CTRM</t>
+    <t>(9/14/26) Castor Maritime Inc. (CTRM)</t>
   </si>
   <si>
     <t>Columbus McKinnon Corporation</t>
@@ -168,6 +168,12 @@
     <t>News Archive for HDSN</t>
   </si>
   <si>
+    <t>Jerash Holdings (US), Inc. *</t>
+  </si>
+  <si>
+    <t>JRSH*</t>
+  </si>
+  <si>
     <t>Kimball Electronics, Inc.</t>
   </si>
   <si>
@@ -204,7 +210,7 @@
     <t>Approaching value limit</t>
   </si>
   <si>
-    <t>News Archive for MG</t>
+    <t>(9/18/26) Mistras Group, Inc. (MG)</t>
   </si>
   <si>
     <t>NACCO Industries, Inc.</t>
@@ -268,6 +274,12 @@
   </si>
   <si>
     <t>News Archive for RCKY</t>
+  </si>
+  <si>
+    <t>Smart Sand, Inc. *</t>
+  </si>
+  <si>
+    <t>SND*</t>
   </si>
   <si>
     <t>Smith Douglas Homes Corp.</t>
@@ -612,7 +624,7 @@
         <v>12</v>
       </c>
       <c r="C2" s="3">
-        <v>5.19</v>
+        <v>5.11</v>
       </c>
       <c r="D2" s="3">
         <v>7.5</v>
@@ -621,16 +633,16 @@
         <v>4.34</v>
       </c>
       <c r="F2" s="2">
-        <v>53.0</v>
+        <v>54.0</v>
       </c>
       <c r="G2" s="2">
-        <v>13.3</v>
+        <v>13.6</v>
       </c>
       <c r="H2" s="3">
-        <v>0.81</v>
+        <v>0.83</v>
       </c>
       <c r="I2" s="4">
-        <v>49.0</v>
+        <v>61.0</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>13</v>
@@ -647,7 +659,7 @@
         <v>16</v>
       </c>
       <c r="C3" s="3">
-        <v>4.93</v>
+        <v>4.5</v>
       </c>
       <c r="D3" s="3">
         <v>6.79</v>
@@ -656,16 +668,16 @@
         <v>3.65</v>
       </c>
       <c r="F3" s="2">
-        <v>204.4</v>
+        <v>189.0</v>
       </c>
       <c r="G3" s="2">
-        <v>10.0</v>
+        <v>9.2</v>
       </c>
       <c r="H3" s="3">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="I3" s="4">
-        <v>24.0</v>
+        <v>18.0</v>
       </c>
       <c r="K3" s="2" t="s">
         <v>17</v>
@@ -679,7 +691,7 @@
         <v>19</v>
       </c>
       <c r="C4" s="3">
-        <v>2.42</v>
+        <v>2.18</v>
       </c>
       <c r="D4" s="3">
         <v>2.66</v>
@@ -688,10 +700,10 @@
         <v>1.66</v>
       </c>
       <c r="F4" s="2">
-        <v>23.4</v>
+        <v>21.4</v>
       </c>
       <c r="G4" s="2">
-        <v>6.7</v>
+        <v>6.2</v>
       </c>
       <c r="H4" s="3">
         <v>0.04</v>
@@ -711,7 +723,7 @@
         <v>22</v>
       </c>
       <c r="C5" s="3">
-        <v>17.74</v>
+        <v>15.76</v>
       </c>
       <c r="D5" s="3">
         <v>24.4</v>
@@ -720,16 +732,16 @@
         <v>11.99</v>
       </c>
       <c r="F5" s="2">
-        <v>506.7</v>
+        <v>449.2</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>23</v>
       </c>
       <c r="H5" s="3">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="I5" s="4">
-        <v>64.0</v>
+        <v>61.0</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -746,7 +758,7 @@
         <v>27</v>
       </c>
       <c r="C6" s="3">
-        <v>23.75</v>
+        <v>24.2</v>
       </c>
       <c r="D6" s="3">
         <v>28.69</v>
@@ -755,16 +767,16 @@
         <v>16.6</v>
       </c>
       <c r="F6" s="2">
-        <v>203.4</v>
+        <v>202.5</v>
       </c>
       <c r="G6" s="2">
-        <v>28.3</v>
+        <v>28.2</v>
       </c>
       <c r="H6" s="3">
         <v>1.22</v>
       </c>
       <c r="I6" s="4">
-        <v>71.0</v>
+        <v>62.0</v>
       </c>
       <c r="K6" s="2" t="s">
         <v>28</v>
@@ -778,7 +790,7 @@
         <v>30</v>
       </c>
       <c r="C7" s="3">
-        <v>35.63</v>
+        <v>33.8</v>
       </c>
       <c r="D7" s="3">
         <v>49.88</v>
@@ -787,16 +799,16 @@
         <v>18.0</v>
       </c>
       <c r="F7" s="2">
-        <v>904.2</v>
+        <v>862.8</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>23</v>
       </c>
       <c r="H7" s="3">
-        <v>2.19</v>
+        <v>2.09</v>
       </c>
       <c r="I7" s="4">
-        <v>87.0</v>
+        <v>82.0</v>
       </c>
       <c r="K7" s="2" t="s">
         <v>31</v>
@@ -810,7 +822,7 @@
         <v>33</v>
       </c>
       <c r="C8" s="3">
-        <v>21.3</v>
+        <v>21.32</v>
       </c>
       <c r="D8" s="3">
         <v>22.94</v>
@@ -819,16 +831,16 @@
         <v>16.3</v>
       </c>
       <c r="F8" s="2">
-        <v>538.9</v>
+        <v>541.1</v>
       </c>
       <c r="G8" s="2">
-        <v>12.7</v>
+        <v>12.8</v>
       </c>
       <c r="H8" s="3">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="I8" s="4">
-        <v>46.0</v>
+        <v>52.0</v>
       </c>
       <c r="K8" s="2" t="s">
         <v>34</v>
@@ -842,7 +854,7 @@
         <v>36</v>
       </c>
       <c r="C9" s="3">
-        <v>19.51</v>
+        <v>19.43</v>
       </c>
       <c r="D9" s="3">
         <v>23.07</v>
@@ -851,7 +863,7 @@
         <v>11.41</v>
       </c>
       <c r="F9" s="2">
-        <v>268.9</v>
+        <v>268.0</v>
       </c>
       <c r="G9" s="2">
         <v>11.7</v>
@@ -860,7 +872,7 @@
         <v>1.47</v>
       </c>
       <c r="I9" s="4">
-        <v>67.0</v>
+        <v>61.0</v>
       </c>
       <c r="K9" s="2" t="s">
         <v>37</v>
@@ -874,7 +886,7 @@
         <v>39</v>
       </c>
       <c r="C10" s="3">
-        <v>74.56</v>
+        <v>77.59</v>
       </c>
       <c r="D10" s="3">
         <v>79.67</v>
@@ -883,16 +895,16 @@
         <v>51.0</v>
       </c>
       <c r="F10" s="2">
-        <v>526.1</v>
+        <v>529.8</v>
       </c>
       <c r="G10" s="2">
         <v>3.9</v>
       </c>
       <c r="H10" s="3">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="I10" s="4">
-        <v>62.0</v>
+        <v>58.0</v>
       </c>
       <c r="K10" s="2" t="s">
         <v>40</v>
@@ -906,7 +918,7 @@
         <v>42</v>
       </c>
       <c r="C11" s="3">
-        <v>43.28</v>
+        <v>41.21</v>
       </c>
       <c r="D11" s="3">
         <v>48.77</v>
@@ -915,13 +927,13 @@
         <v>16.55</v>
       </c>
       <c r="F11" s="2">
-        <v>312.2</v>
+        <v>301.4</v>
       </c>
       <c r="G11" s="2">
-        <v>11.3</v>
+        <v>10.9</v>
       </c>
       <c r="H11" s="3">
-        <v>1.9</v>
+        <v>1.84</v>
       </c>
       <c r="I11" s="4">
         <v>98.0</v>
@@ -938,7 +950,7 @@
         <v>45</v>
       </c>
       <c r="C12" s="3">
-        <v>9.89</v>
+        <v>9.82</v>
       </c>
       <c r="D12" s="3">
         <v>20.93</v>
@@ -947,13 +959,13 @@
         <v>9.37</v>
       </c>
       <c r="F12" s="2">
-        <v>761.8</v>
+        <v>766.4</v>
       </c>
       <c r="G12" s="2">
-        <v>23.5</v>
+        <v>23.6</v>
       </c>
       <c r="H12" s="3">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="I12" s="4">
         <v>11.0</v>
@@ -970,25 +982,25 @@
         <v>48</v>
       </c>
       <c r="C13" s="3">
-        <v>5.41</v>
+        <v>5.17</v>
       </c>
       <c r="D13" s="3">
-        <v>10.52</v>
+        <v>10.3</v>
       </c>
       <c r="E13" s="3">
         <v>4.64</v>
       </c>
       <c r="F13" s="2">
-        <v>227.5</v>
+        <v>216.8</v>
       </c>
       <c r="G13" s="2">
-        <v>26.0</v>
+        <v>24.8</v>
       </c>
       <c r="H13" s="3">
-        <v>0.94</v>
+        <v>0.89</v>
       </c>
       <c r="I13" s="4">
-        <v>37.0</v>
+        <v>28.0</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>13</v>
@@ -1005,492 +1017,554 @@
         <v>51</v>
       </c>
       <c r="C14" s="3">
-        <v>26.17</v>
+        <v>5.64</v>
       </c>
       <c r="D14" s="3">
-        <v>33.19</v>
+        <v>5.81</v>
       </c>
       <c r="E14" s="3">
-        <v>21.01</v>
+        <v>2.85</v>
       </c>
       <c r="F14" s="2">
-        <v>626.6</v>
+        <v>71.4</v>
       </c>
       <c r="G14" s="2">
-        <v>23.1</v>
+        <v>15.3</v>
       </c>
       <c r="H14" s="3">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="I14" s="4">
-        <v>63.0</v>
-      </c>
-      <c r="K14" s="2" t="s">
-        <v>52</v>
+        <v>95.0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B15" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="C15" s="3">
+        <v>24.65</v>
+      </c>
+      <c r="D15" s="3">
+        <v>33.19</v>
+      </c>
+      <c r="E15" s="3">
+        <v>21.01</v>
+      </c>
+      <c r="F15" s="2">
+        <v>600.1</v>
+      </c>
+      <c r="G15" s="2">
+        <v>22.2</v>
+      </c>
+      <c r="H15" s="3">
+        <v>1.03</v>
+      </c>
+      <c r="I15" s="4">
+        <v>56.0</v>
+      </c>
+      <c r="K15" s="2" t="s">
         <v>54</v>
-      </c>
-      <c r="C15" s="3">
-        <v>6.56</v>
-      </c>
-      <c r="D15" s="3">
-        <v>6.88</v>
-      </c>
-      <c r="E15" s="3">
-        <v>3.35</v>
-      </c>
-      <c r="F15" s="2">
-        <v>235.2</v>
-      </c>
-      <c r="G15" s="2">
-        <v>12.2</v>
-      </c>
-      <c r="H15" s="3">
-        <v>1.08</v>
-      </c>
-      <c r="I15" s="4">
-        <v>78.0</v>
-      </c>
-      <c r="K15" s="2" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B16" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="C16" s="3">
+        <v>6.82</v>
+      </c>
+      <c r="D16" s="3">
+        <v>6.94</v>
+      </c>
+      <c r="E16" s="3">
+        <v>3.35</v>
+      </c>
+      <c r="F16" s="2">
+        <v>239.1</v>
+      </c>
+      <c r="G16" s="2">
+        <v>12.4</v>
+      </c>
+      <c r="H16" s="3">
+        <v>1.1</v>
+      </c>
+      <c r="I16" s="4">
+        <v>82.0</v>
+      </c>
+      <c r="K16" s="2" t="s">
         <v>57</v>
-      </c>
-      <c r="C16" s="3">
-        <v>7.47</v>
-      </c>
-      <c r="D16" s="3">
-        <v>8.37</v>
-      </c>
-      <c r="E16" s="3">
-        <v>5.5</v>
-      </c>
-      <c r="F16" s="2">
-        <v>89.7</v>
-      </c>
-      <c r="G16" s="2">
-        <v>44.7</v>
-      </c>
-      <c r="H16" s="3">
-        <v>0.98</v>
-      </c>
-      <c r="I16" s="4">
-        <v>63.0</v>
-      </c>
-      <c r="K16" s="2" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B17" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="C17" s="3">
+        <v>7.22</v>
+      </c>
+      <c r="D17" s="3">
+        <v>8.37</v>
+      </c>
+      <c r="E17" s="3">
+        <v>5.5</v>
+      </c>
+      <c r="F17" s="2">
+        <v>89.3</v>
+      </c>
+      <c r="G17" s="2">
+        <v>44.5</v>
+      </c>
+      <c r="H17" s="3">
+        <v>0.97</v>
+      </c>
+      <c r="I17" s="4">
+        <v>82.0</v>
+      </c>
+      <c r="K17" s="2" t="s">
         <v>60</v>
-      </c>
-      <c r="C17" s="3">
-        <v>19.81</v>
-      </c>
-      <c r="D17" s="3">
-        <v>20.2</v>
-      </c>
-      <c r="E17" s="3">
-        <v>9.35</v>
-      </c>
-      <c r="F17" s="2">
-        <v>630.9</v>
-      </c>
-      <c r="G17" s="2">
-        <v>24.1</v>
-      </c>
-      <c r="H17" s="3">
-        <v>2.63</v>
-      </c>
-      <c r="I17" s="4">
-        <v>84.0</v>
-      </c>
-      <c r="J17" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="K17" s="2" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C18" s="3">
+        <v>20.75</v>
+      </c>
+      <c r="D18" s="3">
+        <v>20.4</v>
+      </c>
+      <c r="E18" s="3">
+        <v>9.37</v>
+      </c>
+      <c r="F18" s="2">
+        <v>631.9</v>
+      </c>
+      <c r="G18" s="2">
+        <v>24.1</v>
+      </c>
+      <c r="H18" s="3">
+        <v>2.63</v>
+      </c>
+      <c r="I18" s="4">
+        <v>85.0</v>
+      </c>
+      <c r="J18" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="B18" s="2" t="s">
+      <c r="K18" s="2" t="s">
         <v>64</v>
-      </c>
-      <c r="C18" s="3">
-        <v>39.7</v>
-      </c>
-      <c r="D18" s="3">
-        <v>59.42</v>
-      </c>
-      <c r="E18" s="3">
-        <v>39.4</v>
-      </c>
-      <c r="F18" s="2">
-        <v>299.6</v>
-      </c>
-      <c r="G18" s="2">
-        <v>17.3</v>
-      </c>
-      <c r="H18" s="3">
-        <v>0.69</v>
-      </c>
-      <c r="I18" s="4">
-        <v>18.0</v>
-      </c>
-      <c r="K18" s="2" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B19" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="C19" s="3">
+        <v>36.91</v>
+      </c>
+      <c r="D19" s="3">
+        <v>59.42</v>
+      </c>
+      <c r="E19" s="3">
+        <v>37.47</v>
+      </c>
+      <c r="F19" s="2">
+        <v>282.8</v>
+      </c>
+      <c r="G19" s="2">
+        <v>16.4</v>
+      </c>
+      <c r="H19" s="3">
+        <v>0.65</v>
+      </c>
+      <c r="I19" s="4">
+        <v>20.0</v>
+      </c>
+      <c r="K19" s="2" t="s">
         <v>67</v>
-      </c>
-      <c r="C19" s="3">
-        <v>37.87</v>
-      </c>
-      <c r="D19" s="3">
-        <v>44.61</v>
-      </c>
-      <c r="E19" s="3">
-        <v>25.53</v>
-      </c>
-      <c r="F19" s="2">
-        <v>488.5</v>
-      </c>
-      <c r="G19" s="2">
-        <v>23.7</v>
-      </c>
-      <c r="H19" s="3">
-        <v>1.66</v>
-      </c>
-      <c r="I19" s="4">
-        <v>52.0</v>
-      </c>
-      <c r="K19" s="2" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="20" ht="15.75" customHeight="1">
       <c r="A20" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B20" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="B20" s="2" t="s">
+      <c r="C20" s="3">
+        <v>35.37</v>
+      </c>
+      <c r="D20" s="3">
+        <v>44.61</v>
+      </c>
+      <c r="E20" s="3">
+        <v>25.53</v>
+      </c>
+      <c r="F20" s="2">
+        <v>462.4</v>
+      </c>
+      <c r="G20" s="2">
+        <v>22.4</v>
+      </c>
+      <c r="H20" s="3">
+        <v>1.57</v>
+      </c>
+      <c r="I20" s="4">
+        <v>40.0</v>
+      </c>
+      <c r="K20" s="2" t="s">
         <v>70</v>
-      </c>
-      <c r="C20" s="3">
-        <v>8.69</v>
-      </c>
-      <c r="D20" s="3">
-        <v>14.5</v>
-      </c>
-      <c r="E20" s="3">
-        <v>5.5</v>
-      </c>
-      <c r="F20" s="2">
-        <v>524.2</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="H20" s="3">
-        <v>0.9</v>
-      </c>
-      <c r="I20" s="4">
-        <v>18.0</v>
-      </c>
-      <c r="J20" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="K20" s="2" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B21" s="2" t="s">
         <v>72</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>73</v>
       </c>
       <c r="C21" s="3">
         <v>8.41</v>
       </c>
       <c r="D21" s="3">
-        <v>9.39</v>
+        <v>14.5</v>
       </c>
       <c r="E21" s="3">
-        <v>4.54</v>
+        <v>5.5</v>
       </c>
       <c r="F21" s="2">
-        <v>550.6</v>
-      </c>
-      <c r="G21" s="2">
-        <v>11.6</v>
+        <v>506.7</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>23</v>
       </c>
       <c r="H21" s="3">
-        <v>1.23</v>
+        <v>0.87</v>
       </c>
       <c r="I21" s="4">
-        <v>68.0</v>
+        <v>16.0</v>
+      </c>
+      <c r="J21" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="B22" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="B22" s="2" t="s">
+      <c r="C22" s="3">
+        <v>8.38</v>
+      </c>
+      <c r="D22" s="3">
+        <v>9.39</v>
+      </c>
+      <c r="E22" s="3">
+        <v>4.54</v>
+      </c>
+      <c r="F22" s="2">
+        <v>550.6</v>
+      </c>
+      <c r="G22" s="2">
+        <v>11.6</v>
+      </c>
+      <c r="H22" s="3">
+        <v>1.23</v>
+      </c>
+      <c r="I22" s="4">
+        <v>70.0</v>
+      </c>
+      <c r="K22" s="2" t="s">
         <v>76</v>
-      </c>
-      <c r="C22" s="3">
-        <v>46.45</v>
-      </c>
-      <c r="D22" s="3">
-        <v>53.3</v>
-      </c>
-      <c r="E22" s="3">
-        <v>18.06</v>
-      </c>
-      <c r="F22" s="2">
-        <v>650.1</v>
-      </c>
-      <c r="G22" s="2">
-        <v>23.9</v>
-      </c>
-      <c r="H22" s="3">
-        <v>1.66</v>
-      </c>
-      <c r="I22" s="4">
-        <v>95.0</v>
-      </c>
-      <c r="K22" s="2" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="B23" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="B23" s="2" t="s">
+      <c r="C23" s="3">
+        <v>46.06</v>
+      </c>
+      <c r="D23" s="3">
+        <v>53.3</v>
+      </c>
+      <c r="E23" s="3">
+        <v>18.06</v>
+      </c>
+      <c r="F23" s="2">
+        <v>646.8</v>
+      </c>
+      <c r="G23" s="2">
+        <v>23.8</v>
+      </c>
+      <c r="H23" s="3">
+        <v>1.65</v>
+      </c>
+      <c r="I23" s="4">
+        <v>96.0</v>
+      </c>
+      <c r="K23" s="2" t="s">
         <v>79</v>
-      </c>
-      <c r="C23" s="3">
-        <v>27.5</v>
-      </c>
-      <c r="D23" s="3">
-        <v>31.5</v>
-      </c>
-      <c r="E23" s="3">
-        <v>19.31</v>
-      </c>
-      <c r="F23" s="2">
-        <v>68.7</v>
-      </c>
-      <c r="G23" s="2">
-        <v>11.4</v>
-      </c>
-      <c r="H23" s="3">
-        <v>0.35</v>
-      </c>
-      <c r="I23" s="4">
-        <v>79.0</v>
-      </c>
-      <c r="J23" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="K23" s="2" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B24" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="B24" s="2" t="s">
+      <c r="C24" s="3">
+        <v>26.71</v>
+      </c>
+      <c r="D24" s="3">
+        <v>31.5</v>
+      </c>
+      <c r="E24" s="3">
+        <v>19.31</v>
+      </c>
+      <c r="F24" s="2">
+        <v>68.2</v>
+      </c>
+      <c r="G24" s="2">
+        <v>11.3</v>
+      </c>
+      <c r="H24" s="3">
+        <v>0.35</v>
+      </c>
+      <c r="I24" s="4">
+        <v>62.0</v>
+      </c>
+      <c r="J24" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="K24" s="2" t="s">
         <v>82</v>
-      </c>
-      <c r="C24" s="3">
-        <v>44.19</v>
-      </c>
-      <c r="D24" s="3">
-        <v>53.01</v>
-      </c>
-      <c r="E24" s="3">
-        <v>26.29</v>
-      </c>
-      <c r="F24" s="2">
-        <v>331.1</v>
-      </c>
-      <c r="G24" s="2">
-        <v>11.6</v>
-      </c>
-      <c r="H24" s="3">
-        <v>1.26</v>
-      </c>
-      <c r="I24" s="4">
-        <v>46.0</v>
-      </c>
-      <c r="K24" s="2" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B25" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="B25" s="2" t="s">
+      <c r="C25" s="3">
+        <v>43.87</v>
+      </c>
+      <c r="D25" s="3">
+        <v>53.01</v>
+      </c>
+      <c r="E25" s="3">
+        <v>26.29</v>
+      </c>
+      <c r="F25" s="2">
+        <v>325.7</v>
+      </c>
+      <c r="G25" s="2">
+        <v>11.4</v>
+      </c>
+      <c r="H25" s="3">
+        <v>1.23</v>
+      </c>
+      <c r="I25" s="4">
+        <v>51.0</v>
+      </c>
+      <c r="K25" s="2" t="s">
         <v>85</v>
-      </c>
-      <c r="C25" s="3">
-        <v>10.58</v>
-      </c>
-      <c r="D25" s="3">
-        <v>23.49</v>
-      </c>
-      <c r="E25" s="3">
-        <v>10.01</v>
-      </c>
-      <c r="F25" s="2">
-        <v>88.8</v>
-      </c>
-      <c r="G25" s="2">
-        <v>14.5</v>
-      </c>
-      <c r="H25" s="3">
-        <v>1.12</v>
-      </c>
-      <c r="I25" s="4">
-        <v>36.0</v>
-      </c>
-      <c r="K25" s="2" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="B26" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="B26" s="2" t="s">
-        <v>88</v>
-      </c>
       <c r="C26" s="3">
-        <v>9.42</v>
+        <v>5.38</v>
       </c>
       <c r="D26" s="3">
-        <v>10.55</v>
+        <v>5.92</v>
       </c>
       <c r="E26" s="3">
-        <v>6.12</v>
+        <v>2.01</v>
       </c>
       <c r="F26" s="2">
-        <v>349.2</v>
+        <v>223.9</v>
       </c>
       <c r="G26" s="2">
-        <v>5.7</v>
+        <v>21.2</v>
       </c>
       <c r="H26" s="3">
-        <v>0.51</v>
+        <v>0.86</v>
       </c>
       <c r="I26" s="4">
-        <v>52.0</v>
+        <v>71.0</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="K26" s="2" t="s">
-        <v>89</v>
-      </c>
     </row>
     <row r="27" ht="15.75" customHeight="1">
       <c r="A27" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C27" s="3">
+        <v>10.04</v>
+      </c>
+      <c r="D27" s="3">
+        <v>23.49</v>
+      </c>
+      <c r="E27" s="3">
+        <v>10.01</v>
+      </c>
+      <c r="F27" s="2">
+        <v>86.0</v>
+      </c>
+      <c r="G27" s="2">
+        <v>14.0</v>
+      </c>
+      <c r="H27" s="3">
+        <v>1.08</v>
+      </c>
+      <c r="I27" s="4">
+        <v>20.0</v>
+      </c>
+      <c r="K27" s="2" t="s">
         <v>90</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="C27" s="3">
-        <v>24.48</v>
-      </c>
-      <c r="D27" s="3">
-        <v>29.91</v>
-      </c>
-      <c r="E27" s="3">
-        <v>17.61</v>
-      </c>
-      <c r="F27" s="2">
-        <v>147.3</v>
-      </c>
-      <c r="G27" s="2">
-        <v>18.5</v>
-      </c>
-      <c r="H27" s="3">
-        <v>1.13</v>
-      </c>
-      <c r="I27" s="4">
-        <v>68.0</v>
-      </c>
-      <c r="K27" s="2" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="C28" s="3">
+        <v>9.46</v>
+      </c>
+      <c r="D28" s="3">
+        <v>10.55</v>
+      </c>
+      <c r="E28" s="3">
+        <v>6.12</v>
+      </c>
+      <c r="F28" s="2">
+        <v>360.0</v>
+      </c>
+      <c r="G28" s="2">
+        <v>5.9</v>
+      </c>
+      <c r="H28" s="3">
+        <v>0.52</v>
+      </c>
+      <c r="I28" s="4">
+        <v>51.0</v>
+      </c>
+      <c r="J28" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="K28" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="B28" s="2" t="s">
+    </row>
+    <row r="29" ht="15.75" customHeight="1">
+      <c r="A29" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="C28" s="3">
-        <v>15.02</v>
-      </c>
-      <c r="D28" s="3">
-        <v>31.15</v>
-      </c>
-      <c r="E28" s="3">
+      <c r="B29" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C29" s="3">
+        <v>25.59</v>
+      </c>
+      <c r="D29" s="3">
+        <v>29.91</v>
+      </c>
+      <c r="E29" s="3">
+        <v>17.61</v>
+      </c>
+      <c r="F29" s="2">
+        <v>148.4</v>
+      </c>
+      <c r="G29" s="2">
+        <v>18.6</v>
+      </c>
+      <c r="H29" s="3">
+        <v>1.14</v>
+      </c>
+      <c r="I29" s="4">
+        <v>72.0</v>
+      </c>
+      <c r="K29" s="2" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="30" ht="15.75" customHeight="1">
+      <c r="A30" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C30" s="3">
+        <v>14.14</v>
+      </c>
+      <c r="D30" s="3">
+        <v>30.93</v>
+      </c>
+      <c r="E30" s="3">
         <v>12.57</v>
       </c>
-      <c r="F28" s="2">
-        <v>277.5</v>
-      </c>
-      <c r="G28" s="2" t="s">
+      <c r="F30" s="2">
+        <v>265.0</v>
+      </c>
+      <c r="G30" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="H28" s="3">
-        <v>0.53</v>
-      </c>
-      <c r="I28" s="4">
-        <v>30.0</v>
-      </c>
-      <c r="K28" s="2" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="29" ht="15.75" customHeight="1"/>
-    <row r="30" ht="15.75" customHeight="1"/>
+      <c r="H30" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="I30" s="4">
+        <v>26.0</v>
+      </c>
+      <c r="J30" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="K30" s="2" t="s">
+        <v>99</v>
+      </c>
+    </row>
     <row r="31" ht="15.75" customHeight="1"/>
     <row r="32" ht="15.75" customHeight="1"/>
     <row r="33" ht="15.75" customHeight="1"/>

--- a/AAII.xlsx
+++ b/AAII.xlsx
@@ -9,7 +9,7 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="wDXvabttsKun171Rni81VIHwM6VhsjY4ECO6QmsPaMk="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="6c+Nu3nbfTK8+mVfJqIv6aWfo9OoM1sOkXoBvSb+crI="/>
     </ext>
   </extLst>
 </workbook>
@@ -78,7 +78,7 @@
     <t>CTRM</t>
   </si>
   <si>
-    <t>(9/14/26) Castor Maritime Inc. (CTRM)</t>
+    <t>News Archive for CTRM</t>
   </si>
   <si>
     <t>Columbus McKinnon Corporation</t>
@@ -210,7 +210,7 @@
     <t>Approaching value limit</t>
   </si>
   <si>
-    <t>(9/18/26) Mistras Group, Inc. (MG)</t>
+    <t>News Archive for MG</t>
   </si>
   <si>
     <t>NACCO Industries, Inc.</t>
@@ -624,7 +624,7 @@
         <v>12</v>
       </c>
       <c r="C2" s="3">
-        <v>5.11</v>
+        <v>5.14</v>
       </c>
       <c r="D2" s="3">
         <v>7.5</v>
@@ -633,16 +633,16 @@
         <v>4.34</v>
       </c>
       <c r="F2" s="2">
-        <v>54.0</v>
+        <v>50.8</v>
       </c>
       <c r="G2" s="2">
-        <v>13.6</v>
+        <v>12.8</v>
       </c>
       <c r="H2" s="3">
-        <v>0.83</v>
+        <v>0.78</v>
       </c>
       <c r="I2" s="4">
-        <v>61.0</v>
+        <v>59.0</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>13</v>
@@ -659,7 +659,7 @@
         <v>16</v>
       </c>
       <c r="C3" s="3">
-        <v>4.5</v>
+        <v>4.28</v>
       </c>
       <c r="D3" s="3">
         <v>6.79</v>
@@ -668,16 +668,16 @@
         <v>3.65</v>
       </c>
       <c r="F3" s="2">
-        <v>189.0</v>
+        <v>179.9</v>
       </c>
       <c r="G3" s="2">
-        <v>9.2</v>
+        <v>8.8</v>
       </c>
       <c r="H3" s="3">
-        <v>0.43</v>
+        <v>0.41</v>
       </c>
       <c r="I3" s="4">
-        <v>18.0</v>
+        <v>14.0</v>
       </c>
       <c r="K3" s="2" t="s">
         <v>17</v>
@@ -691,7 +691,7 @@
         <v>19</v>
       </c>
       <c r="C4" s="3">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="D4" s="3">
         <v>2.66</v>
@@ -700,16 +700,16 @@
         <v>1.66</v>
       </c>
       <c r="F4" s="2">
-        <v>21.4</v>
+        <v>20.7</v>
       </c>
       <c r="G4" s="2">
-        <v>6.2</v>
+        <v>6.0</v>
       </c>
       <c r="H4" s="3">
         <v>0.04</v>
       </c>
       <c r="I4" s="4">
-        <v>60.0</v>
+        <v>63.0</v>
       </c>
       <c r="K4" s="2" t="s">
         <v>20</v>
@@ -723,7 +723,7 @@
         <v>22</v>
       </c>
       <c r="C5" s="3">
-        <v>15.76</v>
+        <v>16.83</v>
       </c>
       <c r="D5" s="3">
         <v>24.4</v>
@@ -732,16 +732,16 @@
         <v>11.99</v>
       </c>
       <c r="F5" s="2">
-        <v>449.2</v>
+        <v>457.5</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>23</v>
       </c>
       <c r="H5" s="3">
-        <v>0.8</v>
+        <v>0.81</v>
       </c>
       <c r="I5" s="4">
-        <v>61.0</v>
+        <v>55.0</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -758,7 +758,7 @@
         <v>27</v>
       </c>
       <c r="C6" s="3">
-        <v>24.2</v>
+        <v>23.21</v>
       </c>
       <c r="D6" s="3">
         <v>28.69</v>
@@ -767,16 +767,16 @@
         <v>16.6</v>
       </c>
       <c r="F6" s="2">
-        <v>202.5</v>
+        <v>197.8</v>
       </c>
       <c r="G6" s="2">
-        <v>28.2</v>
+        <v>27.5</v>
       </c>
       <c r="H6" s="3">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="I6" s="4">
-        <v>62.0</v>
+        <v>61.0</v>
       </c>
       <c r="K6" s="2" t="s">
         <v>28</v>
@@ -790,7 +790,7 @@
         <v>30</v>
       </c>
       <c r="C7" s="3">
-        <v>33.8</v>
+        <v>32.47</v>
       </c>
       <c r="D7" s="3">
         <v>49.88</v>
@@ -799,16 +799,16 @@
         <v>18.0</v>
       </c>
       <c r="F7" s="2">
-        <v>862.8</v>
+        <v>841.5</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>23</v>
       </c>
       <c r="H7" s="3">
-        <v>2.09</v>
+        <v>2.04</v>
       </c>
       <c r="I7" s="4">
-        <v>82.0</v>
+        <v>73.0</v>
       </c>
       <c r="K7" s="2" t="s">
         <v>31</v>
@@ -822,7 +822,7 @@
         <v>33</v>
       </c>
       <c r="C8" s="3">
-        <v>21.32</v>
+        <v>22.13</v>
       </c>
       <c r="D8" s="3">
         <v>22.94</v>
@@ -831,16 +831,16 @@
         <v>16.3</v>
       </c>
       <c r="F8" s="2">
-        <v>541.1</v>
+        <v>564.4</v>
       </c>
       <c r="G8" s="2">
-        <v>12.8</v>
+        <v>13.4</v>
       </c>
       <c r="H8" s="3">
-        <v>1.74</v>
+        <v>1.81</v>
       </c>
       <c r="I8" s="4">
-        <v>52.0</v>
+        <v>53.0</v>
       </c>
       <c r="K8" s="2" t="s">
         <v>34</v>
@@ -854,7 +854,7 @@
         <v>36</v>
       </c>
       <c r="C9" s="3">
-        <v>19.43</v>
+        <v>19.52</v>
       </c>
       <c r="D9" s="3">
         <v>23.07</v>
@@ -863,16 +863,16 @@
         <v>11.41</v>
       </c>
       <c r="F9" s="2">
-        <v>268.0</v>
+        <v>265.8</v>
       </c>
       <c r="G9" s="2">
-        <v>11.7</v>
+        <v>11.6</v>
       </c>
       <c r="H9" s="3">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="I9" s="4">
-        <v>61.0</v>
+        <v>58.0</v>
       </c>
       <c r="K9" s="2" t="s">
         <v>37</v>
@@ -886,7 +886,7 @@
         <v>39</v>
       </c>
       <c r="C10" s="3">
-        <v>77.59</v>
+        <v>69.7</v>
       </c>
       <c r="D10" s="3">
         <v>79.67</v>
@@ -895,16 +895,16 @@
         <v>51.0</v>
       </c>
       <c r="F10" s="2">
-        <v>529.8</v>
+        <v>501.2</v>
       </c>
       <c r="G10" s="2">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="H10" s="3">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="I10" s="4">
-        <v>58.0</v>
+        <v>64.0</v>
       </c>
       <c r="K10" s="2" t="s">
         <v>40</v>
@@ -918,7 +918,7 @@
         <v>42</v>
       </c>
       <c r="C11" s="3">
-        <v>41.21</v>
+        <v>39.34</v>
       </c>
       <c r="D11" s="3">
         <v>48.77</v>
@@ -927,16 +927,16 @@
         <v>16.55</v>
       </c>
       <c r="F11" s="2">
-        <v>301.4</v>
+        <v>284.7</v>
       </c>
       <c r="G11" s="2">
-        <v>10.9</v>
+        <v>10.3</v>
       </c>
       <c r="H11" s="3">
-        <v>1.84</v>
+        <v>1.73</v>
       </c>
       <c r="I11" s="4">
-        <v>98.0</v>
+        <v>97.0</v>
       </c>
       <c r="K11" s="2" t="s">
         <v>43</v>
@@ -950,7 +950,7 @@
         <v>45</v>
       </c>
       <c r="C12" s="3">
-        <v>9.82</v>
+        <v>10.14</v>
       </c>
       <c r="D12" s="3">
         <v>20.93</v>
@@ -959,13 +959,13 @@
         <v>9.37</v>
       </c>
       <c r="F12" s="2">
-        <v>766.4</v>
+        <v>771.8</v>
       </c>
       <c r="G12" s="2">
-        <v>23.6</v>
+        <v>23.8</v>
       </c>
       <c r="H12" s="3">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="I12" s="4">
         <v>11.0</v>
@@ -982,22 +982,22 @@
         <v>48</v>
       </c>
       <c r="C13" s="3">
-        <v>5.17</v>
+        <v>5.16</v>
       </c>
       <c r="D13" s="3">
-        <v>10.3</v>
+        <v>10.06</v>
       </c>
       <c r="E13" s="3">
         <v>4.64</v>
       </c>
       <c r="F13" s="2">
-        <v>216.8</v>
+        <v>220.1</v>
       </c>
       <c r="G13" s="2">
-        <v>24.8</v>
+        <v>25.1</v>
       </c>
       <c r="H13" s="3">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="I13" s="4">
         <v>28.0</v>
@@ -1017,7 +1017,7 @@
         <v>51</v>
       </c>
       <c r="C14" s="3">
-        <v>5.64</v>
+        <v>5.68</v>
       </c>
       <c r="D14" s="3">
         <v>5.81</v>
@@ -1026,13 +1026,13 @@
         <v>2.85</v>
       </c>
       <c r="F14" s="2">
-        <v>71.4</v>
+        <v>72.3</v>
       </c>
       <c r="G14" s="2">
-        <v>15.3</v>
+        <v>15.5</v>
       </c>
       <c r="H14" s="3">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="I14" s="4">
         <v>95.0</v>
@@ -1046,25 +1046,25 @@
         <v>53</v>
       </c>
       <c r="C15" s="3">
-        <v>24.65</v>
+        <v>27.27</v>
       </c>
       <c r="D15" s="3">
-        <v>33.19</v>
+        <v>32.0</v>
       </c>
       <c r="E15" s="3">
         <v>21.01</v>
       </c>
       <c r="F15" s="2">
-        <v>600.1</v>
+        <v>658.6</v>
       </c>
       <c r="G15" s="2">
-        <v>22.2</v>
+        <v>24.3</v>
       </c>
       <c r="H15" s="3">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="I15" s="4">
-        <v>56.0</v>
+        <v>57.0</v>
       </c>
       <c r="K15" s="2" t="s">
         <v>54</v>
@@ -1078,7 +1078,7 @@
         <v>56</v>
       </c>
       <c r="C16" s="3">
-        <v>6.82</v>
+        <v>6.35</v>
       </c>
       <c r="D16" s="3">
         <v>6.94</v>
@@ -1087,16 +1087,16 @@
         <v>3.35</v>
       </c>
       <c r="F16" s="2">
-        <v>239.1</v>
+        <v>236.4</v>
       </c>
       <c r="G16" s="2">
-        <v>12.4</v>
+        <v>12.2</v>
       </c>
       <c r="H16" s="3">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="I16" s="4">
-        <v>82.0</v>
+        <v>73.0</v>
       </c>
       <c r="K16" s="2" t="s">
         <v>57</v>
@@ -1110,7 +1110,7 @@
         <v>59</v>
       </c>
       <c r="C17" s="3">
-        <v>7.22</v>
+        <v>7.35</v>
       </c>
       <c r="D17" s="3">
         <v>8.37</v>
@@ -1119,16 +1119,16 @@
         <v>5.5</v>
       </c>
       <c r="F17" s="2">
-        <v>89.3</v>
+        <v>86.7</v>
       </c>
       <c r="G17" s="2">
-        <v>44.5</v>
+        <v>43.2</v>
       </c>
       <c r="H17" s="3">
-        <v>0.97</v>
+        <v>0.95</v>
       </c>
       <c r="I17" s="4">
-        <v>82.0</v>
+        <v>66.0</v>
       </c>
       <c r="K17" s="2" t="s">
         <v>60</v>
@@ -1142,25 +1142,25 @@
         <v>62</v>
       </c>
       <c r="C18" s="3">
-        <v>20.75</v>
+        <v>21.52</v>
       </c>
       <c r="D18" s="3">
-        <v>20.4</v>
+        <v>21.57</v>
       </c>
       <c r="E18" s="3">
         <v>9.37</v>
       </c>
       <c r="F18" s="2">
-        <v>631.9</v>
+        <v>681.0</v>
       </c>
       <c r="G18" s="2">
-        <v>24.1</v>
+        <v>26.0</v>
       </c>
       <c r="H18" s="3">
-        <v>2.63</v>
+        <v>2.84</v>
       </c>
       <c r="I18" s="4">
-        <v>85.0</v>
+        <v>86.0</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>63</v>
@@ -1177,25 +1177,25 @@
         <v>66</v>
       </c>
       <c r="C19" s="3">
-        <v>36.91</v>
+        <v>37.67</v>
       </c>
       <c r="D19" s="3">
         <v>59.42</v>
       </c>
       <c r="E19" s="3">
-        <v>37.47</v>
+        <v>36.03</v>
       </c>
       <c r="F19" s="2">
-        <v>282.8</v>
+        <v>284.7</v>
       </c>
       <c r="G19" s="2">
-        <v>16.4</v>
+        <v>16.5</v>
       </c>
       <c r="H19" s="3">
         <v>0.65</v>
       </c>
       <c r="I19" s="4">
-        <v>20.0</v>
+        <v>19.0</v>
       </c>
       <c r="K19" s="2" t="s">
         <v>67</v>
@@ -1209,7 +1209,7 @@
         <v>69</v>
       </c>
       <c r="C20" s="3">
-        <v>35.37</v>
+        <v>32.8</v>
       </c>
       <c r="D20" s="3">
         <v>44.61</v>
@@ -1218,16 +1218,16 @@
         <v>25.53</v>
       </c>
       <c r="F20" s="2">
-        <v>462.4</v>
+        <v>429.5</v>
       </c>
       <c r="G20" s="2">
-        <v>22.4</v>
+        <v>20.8</v>
       </c>
       <c r="H20" s="3">
-        <v>1.57</v>
+        <v>1.46</v>
       </c>
       <c r="I20" s="4">
-        <v>40.0</v>
+        <v>28.0</v>
       </c>
       <c r="K20" s="2" t="s">
         <v>70</v>
@@ -1241,7 +1241,7 @@
         <v>72</v>
       </c>
       <c r="C21" s="3">
-        <v>8.41</v>
+        <v>8.28</v>
       </c>
       <c r="D21" s="3">
         <v>14.5</v>
@@ -1250,13 +1250,13 @@
         <v>5.5</v>
       </c>
       <c r="F21" s="2">
-        <v>506.7</v>
+        <v>501.3</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>23</v>
       </c>
       <c r="H21" s="3">
-        <v>0.87</v>
+        <v>0.86</v>
       </c>
       <c r="I21" s="4">
         <v>16.0</v>
@@ -1276,7 +1276,7 @@
         <v>75</v>
       </c>
       <c r="C22" s="3">
-        <v>8.38</v>
+        <v>8.01</v>
       </c>
       <c r="D22" s="3">
         <v>9.39</v>
@@ -1285,16 +1285,16 @@
         <v>4.54</v>
       </c>
       <c r="F22" s="2">
-        <v>550.6</v>
+        <v>533.6</v>
       </c>
       <c r="G22" s="2">
-        <v>11.6</v>
+        <v>11.2</v>
       </c>
       <c r="H22" s="3">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="I22" s="4">
-        <v>70.0</v>
+        <v>69.0</v>
       </c>
       <c r="K22" s="2" t="s">
         <v>76</v>
@@ -1308,7 +1308,7 @@
         <v>78</v>
       </c>
       <c r="C23" s="3">
-        <v>46.06</v>
+        <v>48.04</v>
       </c>
       <c r="D23" s="3">
         <v>53.3</v>
@@ -1317,13 +1317,13 @@
         <v>18.06</v>
       </c>
       <c r="F23" s="2">
-        <v>646.8</v>
+        <v>665.5</v>
       </c>
       <c r="G23" s="2">
-        <v>23.8</v>
+        <v>24.5</v>
       </c>
       <c r="H23" s="3">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="I23" s="4">
         <v>96.0</v>
@@ -1340,7 +1340,7 @@
         <v>81</v>
       </c>
       <c r="C24" s="3">
-        <v>26.71</v>
+        <v>28.37</v>
       </c>
       <c r="D24" s="3">
         <v>31.5</v>
@@ -1349,16 +1349,16 @@
         <v>19.31</v>
       </c>
       <c r="F24" s="2">
-        <v>68.2</v>
+        <v>71.3</v>
       </c>
       <c r="G24" s="2">
-        <v>11.3</v>
+        <v>11.8</v>
       </c>
       <c r="H24" s="3">
-        <v>0.35</v>
+        <v>0.37</v>
       </c>
       <c r="I24" s="4">
-        <v>62.0</v>
+        <v>68.0</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>13</v>
@@ -1375,7 +1375,7 @@
         <v>84</v>
       </c>
       <c r="C25" s="3">
-        <v>43.87</v>
+        <v>45.1</v>
       </c>
       <c r="D25" s="3">
         <v>53.01</v>
@@ -1384,16 +1384,16 @@
         <v>26.29</v>
       </c>
       <c r="F25" s="2">
-        <v>325.7</v>
+        <v>334.7</v>
       </c>
       <c r="G25" s="2">
-        <v>11.4</v>
+        <v>11.7</v>
       </c>
       <c r="H25" s="3">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="I25" s="4">
-        <v>51.0</v>
+        <v>66.0</v>
       </c>
       <c r="K25" s="2" t="s">
         <v>85</v>
@@ -1407,25 +1407,25 @@
         <v>87</v>
       </c>
       <c r="C26" s="3">
-        <v>5.38</v>
+        <v>5.23</v>
       </c>
       <c r="D26" s="3">
         <v>5.92</v>
       </c>
       <c r="E26" s="3">
-        <v>2.01</v>
+        <v>2.03</v>
       </c>
       <c r="F26" s="2">
-        <v>223.9</v>
+        <v>215.4</v>
       </c>
       <c r="G26" s="2">
-        <v>21.2</v>
+        <v>20.4</v>
       </c>
       <c r="H26" s="3">
-        <v>0.86</v>
+        <v>0.83</v>
       </c>
       <c r="I26" s="4">
-        <v>71.0</v>
+        <v>50.0</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>13</v>
@@ -1439,25 +1439,25 @@
         <v>89</v>
       </c>
       <c r="C27" s="3">
-        <v>10.04</v>
+        <v>10.28</v>
       </c>
       <c r="D27" s="3">
         <v>23.49</v>
       </c>
       <c r="E27" s="3">
-        <v>10.01</v>
+        <v>9.75</v>
       </c>
       <c r="F27" s="2">
-        <v>86.0</v>
+        <v>88.1</v>
       </c>
       <c r="G27" s="2">
-        <v>14.0</v>
+        <v>14.4</v>
       </c>
       <c r="H27" s="3">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="I27" s="4">
-        <v>20.0</v>
+        <v>29.0</v>
       </c>
       <c r="K27" s="2" t="s">
         <v>90</v>
@@ -1471,7 +1471,7 @@
         <v>92</v>
       </c>
       <c r="C28" s="3">
-        <v>9.46</v>
+        <v>8.89</v>
       </c>
       <c r="D28" s="3">
         <v>10.55</v>
@@ -1480,16 +1480,16 @@
         <v>6.12</v>
       </c>
       <c r="F28" s="2">
-        <v>360.0</v>
+        <v>332.1</v>
       </c>
       <c r="G28" s="2">
-        <v>5.9</v>
+        <v>5.4</v>
       </c>
       <c r="H28" s="3">
-        <v>0.52</v>
+        <v>0.48</v>
       </c>
       <c r="I28" s="4">
-        <v>51.0</v>
+        <v>42.0</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>13</v>
@@ -1506,7 +1506,7 @@
         <v>95</v>
       </c>
       <c r="C29" s="3">
-        <v>25.59</v>
+        <v>24.1</v>
       </c>
       <c r="D29" s="3">
         <v>29.91</v>
@@ -1515,16 +1515,16 @@
         <v>17.61</v>
       </c>
       <c r="F29" s="2">
-        <v>148.4</v>
+        <v>146.9</v>
       </c>
       <c r="G29" s="2">
-        <v>18.6</v>
+        <v>18.4</v>
       </c>
       <c r="H29" s="3">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="I29" s="4">
-        <v>72.0</v>
+        <v>75.0</v>
       </c>
       <c r="K29" s="2" t="s">
         <v>96</v>
@@ -1538,16 +1538,16 @@
         <v>98</v>
       </c>
       <c r="C30" s="3">
-        <v>14.14</v>
+        <v>14.5</v>
       </c>
       <c r="D30" s="3">
-        <v>30.93</v>
+        <v>28.97</v>
       </c>
       <c r="E30" s="3">
         <v>12.57</v>
       </c>
       <c r="F30" s="2">
-        <v>265.0</v>
+        <v>263.5</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>23</v>
@@ -1556,7 +1556,7 @@
         <v>0.5</v>
       </c>
       <c r="I30" s="4">
-        <v>26.0</v>
+        <v>27.0</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>

--- a/AAII.xlsx
+++ b/AAII.xlsx
@@ -9,14 +9,14 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="6c+Nu3nbfTK8+mVfJqIv6aWfo9OoM1sOkXoBvSb+crI="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="lWQN1s3ZBhtXq72gqecZAxt6/OFVzTKZDPKYqIk6YC4="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="100">
   <si>
     <t>Company</t>
   </si>
@@ -624,7 +624,7 @@
         <v>12</v>
       </c>
       <c r="C2" s="3">
-        <v>5.14</v>
+        <v>5.09</v>
       </c>
       <c r="D2" s="3">
         <v>7.5</v>
@@ -633,13 +633,13 @@
         <v>4.34</v>
       </c>
       <c r="F2" s="2">
-        <v>50.8</v>
+        <v>51.7</v>
       </c>
       <c r="G2" s="2">
-        <v>12.8</v>
+        <v>13.0</v>
       </c>
       <c r="H2" s="3">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="I2" s="4">
         <v>59.0</v>
@@ -659,7 +659,7 @@
         <v>16</v>
       </c>
       <c r="C3" s="3">
-        <v>4.28</v>
+        <v>4.36</v>
       </c>
       <c r="D3" s="3">
         <v>6.79</v>
@@ -668,16 +668,16 @@
         <v>3.65</v>
       </c>
       <c r="F3" s="2">
-        <v>179.9</v>
+        <v>181.6</v>
       </c>
       <c r="G3" s="2">
-        <v>8.8</v>
+        <v>8.9</v>
       </c>
       <c r="H3" s="3">
         <v>0.41</v>
       </c>
       <c r="I3" s="4">
-        <v>14.0</v>
+        <v>20.0</v>
       </c>
       <c r="K3" s="2" t="s">
         <v>17</v>
@@ -691,7 +691,7 @@
         <v>19</v>
       </c>
       <c r="C4" s="3">
-        <v>2.14</v>
+        <v>2.0</v>
       </c>
       <c r="D4" s="3">
         <v>2.66</v>
@@ -700,16 +700,16 @@
         <v>1.66</v>
       </c>
       <c r="F4" s="2">
-        <v>20.7</v>
+        <v>19.5</v>
       </c>
       <c r="G4" s="2">
-        <v>6.0</v>
+        <v>1.5</v>
       </c>
       <c r="H4" s="3">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="I4" s="4">
-        <v>63.0</v>
+        <v>64.0</v>
       </c>
       <c r="K4" s="2" t="s">
         <v>20</v>
@@ -723,7 +723,7 @@
         <v>22</v>
       </c>
       <c r="C5" s="3">
-        <v>16.83</v>
+        <v>16.74</v>
       </c>
       <c r="D5" s="3">
         <v>24.4</v>
@@ -732,7 +732,7 @@
         <v>11.99</v>
       </c>
       <c r="F5" s="2">
-        <v>457.5</v>
+        <v>454.8</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>23</v>
@@ -741,7 +741,7 @@
         <v>0.81</v>
       </c>
       <c r="I5" s="4">
-        <v>55.0</v>
+        <v>64.0</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -758,7 +758,7 @@
         <v>27</v>
       </c>
       <c r="C6" s="3">
-        <v>23.21</v>
+        <v>23.02</v>
       </c>
       <c r="D6" s="3">
         <v>28.69</v>
@@ -767,16 +767,16 @@
         <v>16.6</v>
       </c>
       <c r="F6" s="2">
-        <v>197.8</v>
+        <v>196.5</v>
       </c>
       <c r="G6" s="2">
-        <v>27.5</v>
+        <v>27.4</v>
       </c>
       <c r="H6" s="3">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="I6" s="4">
-        <v>61.0</v>
+        <v>53.0</v>
       </c>
       <c r="K6" s="2" t="s">
         <v>28</v>
@@ -790,7 +790,7 @@
         <v>30</v>
       </c>
       <c r="C7" s="3">
-        <v>32.47</v>
+        <v>33.76</v>
       </c>
       <c r="D7" s="3">
         <v>49.88</v>
@@ -799,13 +799,13 @@
         <v>18.0</v>
       </c>
       <c r="F7" s="2">
-        <v>841.5</v>
+        <v>839.5</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>23</v>
       </c>
       <c r="H7" s="3">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="I7" s="4">
         <v>73.0</v>
@@ -822,7 +822,7 @@
         <v>33</v>
       </c>
       <c r="C8" s="3">
-        <v>22.13</v>
+        <v>22.56</v>
       </c>
       <c r="D8" s="3">
         <v>22.94</v>
@@ -831,16 +831,16 @@
         <v>16.3</v>
       </c>
       <c r="F8" s="2">
-        <v>564.4</v>
+        <v>570.5</v>
       </c>
       <c r="G8" s="2">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="H8" s="3">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="I8" s="4">
-        <v>53.0</v>
+        <v>55.0</v>
       </c>
       <c r="K8" s="2" t="s">
         <v>34</v>
@@ -854,7 +854,7 @@
         <v>36</v>
       </c>
       <c r="C9" s="3">
-        <v>19.52</v>
+        <v>19.26</v>
       </c>
       <c r="D9" s="3">
         <v>23.07</v>
@@ -863,16 +863,16 @@
         <v>11.41</v>
       </c>
       <c r="F9" s="2">
-        <v>265.8</v>
+        <v>263.5</v>
       </c>
       <c r="G9" s="2">
-        <v>11.6</v>
+        <v>11.5</v>
       </c>
       <c r="H9" s="3">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="I9" s="4">
-        <v>58.0</v>
+        <v>57.0</v>
       </c>
       <c r="K9" s="2" t="s">
         <v>37</v>
@@ -886,7 +886,7 @@
         <v>39</v>
       </c>
       <c r="C10" s="3">
-        <v>69.7</v>
+        <v>72.42</v>
       </c>
       <c r="D10" s="3">
         <v>79.67</v>
@@ -895,16 +895,16 @@
         <v>51.0</v>
       </c>
       <c r="F10" s="2">
-        <v>501.2</v>
+        <v>497.5</v>
       </c>
       <c r="G10" s="2">
         <v>3.7</v>
       </c>
       <c r="H10" s="3">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="I10" s="4">
-        <v>64.0</v>
+        <v>56.0</v>
       </c>
       <c r="K10" s="2" t="s">
         <v>40</v>
@@ -918,7 +918,7 @@
         <v>42</v>
       </c>
       <c r="C11" s="3">
-        <v>39.34</v>
+        <v>41.08</v>
       </c>
       <c r="D11" s="3">
         <v>48.77</v>
@@ -927,13 +927,13 @@
         <v>16.55</v>
       </c>
       <c r="F11" s="2">
-        <v>284.7</v>
+        <v>285.8</v>
       </c>
       <c r="G11" s="2">
         <v>10.3</v>
       </c>
       <c r="H11" s="3">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="I11" s="4">
         <v>97.0</v>
@@ -950,7 +950,7 @@
         <v>45</v>
       </c>
       <c r="C12" s="3">
-        <v>10.14</v>
+        <v>10.03</v>
       </c>
       <c r="D12" s="3">
         <v>20.93</v>
@@ -959,16 +959,16 @@
         <v>9.37</v>
       </c>
       <c r="F12" s="2">
-        <v>771.8</v>
+        <v>758.0</v>
       </c>
       <c r="G12" s="2">
-        <v>23.8</v>
+        <v>23.4</v>
       </c>
       <c r="H12" s="3">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="I12" s="4">
-        <v>11.0</v>
+        <v>13.0</v>
       </c>
       <c r="K12" s="2" t="s">
         <v>46</v>
@@ -982,25 +982,25 @@
         <v>48</v>
       </c>
       <c r="C13" s="3">
-        <v>5.16</v>
+        <v>5.23</v>
       </c>
       <c r="D13" s="3">
-        <v>10.06</v>
+        <v>9.75</v>
       </c>
       <c r="E13" s="3">
         <v>4.64</v>
       </c>
       <c r="F13" s="2">
-        <v>220.1</v>
+        <v>221.0</v>
       </c>
       <c r="G13" s="2">
-        <v>25.1</v>
+        <v>25.2</v>
       </c>
       <c r="H13" s="3">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="I13" s="4">
-        <v>28.0</v>
+        <v>37.0</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>13</v>
@@ -1017,25 +1017,25 @@
         <v>51</v>
       </c>
       <c r="C14" s="3">
-        <v>5.68</v>
+        <v>6.15</v>
       </c>
       <c r="D14" s="3">
-        <v>5.81</v>
+        <v>5.97</v>
       </c>
       <c r="E14" s="3">
         <v>2.85</v>
       </c>
       <c r="F14" s="2">
-        <v>72.3</v>
+        <v>74.0</v>
       </c>
       <c r="G14" s="2">
-        <v>15.5</v>
+        <v>15.8</v>
       </c>
       <c r="H14" s="3">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="I14" s="4">
-        <v>95.0</v>
+        <v>96.0</v>
       </c>
     </row>
     <row r="15">
@@ -1046,7 +1046,7 @@
         <v>53</v>
       </c>
       <c r="C15" s="3">
-        <v>27.27</v>
+        <v>28.79</v>
       </c>
       <c r="D15" s="3">
         <v>32.0</v>
@@ -1055,16 +1055,16 @@
         <v>21.01</v>
       </c>
       <c r="F15" s="2">
-        <v>658.6</v>
+        <v>678.5</v>
       </c>
       <c r="G15" s="2">
-        <v>24.3</v>
+        <v>25.1</v>
       </c>
       <c r="H15" s="3">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="I15" s="4">
-        <v>57.0</v>
+        <v>73.0</v>
       </c>
       <c r="K15" s="2" t="s">
         <v>54</v>
@@ -1078,7 +1078,7 @@
         <v>56</v>
       </c>
       <c r="C16" s="3">
-        <v>6.35</v>
+        <v>6.16</v>
       </c>
       <c r="D16" s="3">
         <v>6.94</v>
@@ -1087,16 +1087,19 @@
         <v>3.35</v>
       </c>
       <c r="F16" s="2">
-        <v>236.4</v>
+        <v>219.2</v>
       </c>
       <c r="G16" s="2">
-        <v>12.2</v>
+        <v>11.4</v>
       </c>
       <c r="H16" s="3">
-        <v>1.08</v>
+        <v>1.0</v>
       </c>
       <c r="I16" s="4">
-        <v>73.0</v>
+        <v>74.0</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="K16" s="2" t="s">
         <v>57</v>
@@ -1110,7 +1113,7 @@
         <v>59</v>
       </c>
       <c r="C17" s="3">
-        <v>7.35</v>
+        <v>7.15</v>
       </c>
       <c r="D17" s="3">
         <v>8.37</v>
@@ -1119,16 +1122,16 @@
         <v>5.5</v>
       </c>
       <c r="F17" s="2">
-        <v>86.7</v>
+        <v>87.3</v>
       </c>
       <c r="G17" s="2">
-        <v>43.2</v>
+        <v>43.5</v>
       </c>
       <c r="H17" s="3">
         <v>0.95</v>
       </c>
       <c r="I17" s="4">
-        <v>66.0</v>
+        <v>79.0</v>
       </c>
       <c r="K17" s="2" t="s">
         <v>60</v>
@@ -1142,25 +1145,25 @@
         <v>62</v>
       </c>
       <c r="C18" s="3">
-        <v>21.52</v>
+        <v>20.65</v>
       </c>
       <c r="D18" s="3">
-        <v>21.57</v>
+        <v>21.77</v>
       </c>
       <c r="E18" s="3">
         <v>9.37</v>
       </c>
       <c r="F18" s="2">
-        <v>681.0</v>
+        <v>657.1</v>
       </c>
       <c r="G18" s="2">
-        <v>26.0</v>
+        <v>25.1</v>
       </c>
       <c r="H18" s="3">
-        <v>2.84</v>
+        <v>2.74</v>
       </c>
       <c r="I18" s="4">
-        <v>86.0</v>
+        <v>84.0</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>63</v>
@@ -1177,25 +1180,25 @@
         <v>66</v>
       </c>
       <c r="C19" s="3">
-        <v>37.67</v>
+        <v>36.25</v>
       </c>
       <c r="D19" s="3">
         <v>59.42</v>
       </c>
       <c r="E19" s="3">
-        <v>36.03</v>
+        <v>35.45</v>
       </c>
       <c r="F19" s="2">
-        <v>284.7</v>
+        <v>274.5</v>
       </c>
       <c r="G19" s="2">
-        <v>16.5</v>
+        <v>15.9</v>
       </c>
       <c r="H19" s="3">
-        <v>0.65</v>
+        <v>0.63</v>
       </c>
       <c r="I19" s="4">
-        <v>19.0</v>
+        <v>18.0</v>
       </c>
       <c r="K19" s="2" t="s">
         <v>67</v>
@@ -1209,7 +1212,7 @@
         <v>69</v>
       </c>
       <c r="C20" s="3">
-        <v>32.8</v>
+        <v>33.17</v>
       </c>
       <c r="D20" s="3">
         <v>44.61</v>
@@ -1218,16 +1221,16 @@
         <v>25.53</v>
       </c>
       <c r="F20" s="2">
-        <v>429.5</v>
+        <v>422.4</v>
       </c>
       <c r="G20" s="2">
-        <v>20.8</v>
+        <v>20.5</v>
       </c>
       <c r="H20" s="3">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="I20" s="4">
-        <v>28.0</v>
+        <v>34.0</v>
       </c>
       <c r="K20" s="2" t="s">
         <v>70</v>
@@ -1241,7 +1244,7 @@
         <v>72</v>
       </c>
       <c r="C21" s="3">
-        <v>8.28</v>
+        <v>8.23</v>
       </c>
       <c r="D21" s="3">
         <v>14.5</v>
@@ -1250,16 +1253,16 @@
         <v>5.5</v>
       </c>
       <c r="F21" s="2">
-        <v>501.3</v>
+        <v>494.0</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>23</v>
       </c>
       <c r="H21" s="3">
-        <v>0.86</v>
+        <v>0.85</v>
       </c>
       <c r="I21" s="4">
-        <v>16.0</v>
+        <v>20.0</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -1276,7 +1279,7 @@
         <v>75</v>
       </c>
       <c r="C22" s="3">
-        <v>8.01</v>
+        <v>8.43</v>
       </c>
       <c r="D22" s="3">
         <v>9.39</v>
@@ -1285,16 +1288,16 @@
         <v>4.54</v>
       </c>
       <c r="F22" s="2">
-        <v>533.6</v>
+        <v>550.6</v>
       </c>
       <c r="G22" s="2">
-        <v>11.2</v>
+        <v>11.6</v>
       </c>
       <c r="H22" s="3">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="I22" s="4">
-        <v>69.0</v>
+        <v>71.0</v>
       </c>
       <c r="K22" s="2" t="s">
         <v>76</v>
@@ -1308,7 +1311,7 @@
         <v>78</v>
       </c>
       <c r="C23" s="3">
-        <v>48.04</v>
+        <v>47.37</v>
       </c>
       <c r="D23" s="3">
         <v>53.3</v>
@@ -1317,13 +1320,13 @@
         <v>18.06</v>
       </c>
       <c r="F23" s="2">
-        <v>665.5</v>
+        <v>651.8</v>
       </c>
       <c r="G23" s="2">
-        <v>24.5</v>
+        <v>24.0</v>
       </c>
       <c r="H23" s="3">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="I23" s="4">
         <v>96.0</v>
@@ -1340,7 +1343,7 @@
         <v>81</v>
       </c>
       <c r="C24" s="3">
-        <v>28.37</v>
+        <v>29.05</v>
       </c>
       <c r="D24" s="3">
         <v>31.5</v>
@@ -1349,16 +1352,16 @@
         <v>19.31</v>
       </c>
       <c r="F24" s="2">
-        <v>71.3</v>
+        <v>73.5</v>
       </c>
       <c r="G24" s="2">
-        <v>11.8</v>
+        <v>12.2</v>
       </c>
       <c r="H24" s="3">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="I24" s="4">
-        <v>68.0</v>
+        <v>73.0</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>13</v>
@@ -1375,7 +1378,7 @@
         <v>84</v>
       </c>
       <c r="C25" s="3">
-        <v>45.1</v>
+        <v>46.74</v>
       </c>
       <c r="D25" s="3">
         <v>53.01</v>
@@ -1384,16 +1387,16 @@
         <v>26.29</v>
       </c>
       <c r="F25" s="2">
-        <v>334.7</v>
+        <v>344.6</v>
       </c>
       <c r="G25" s="2">
-        <v>11.7</v>
+        <v>12.1</v>
       </c>
       <c r="H25" s="3">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="I25" s="4">
-        <v>66.0</v>
+        <v>73.0</v>
       </c>
       <c r="K25" s="2" t="s">
         <v>85</v>
@@ -1407,7 +1410,7 @@
         <v>87</v>
       </c>
       <c r="C26" s="3">
-        <v>5.23</v>
+        <v>5.34</v>
       </c>
       <c r="D26" s="3">
         <v>5.92</v>
@@ -1416,16 +1419,16 @@
         <v>2.03</v>
       </c>
       <c r="F26" s="2">
-        <v>215.4</v>
+        <v>218.8</v>
       </c>
       <c r="G26" s="2">
-        <v>20.4</v>
+        <v>20.7</v>
       </c>
       <c r="H26" s="3">
-        <v>0.83</v>
+        <v>0.84</v>
       </c>
       <c r="I26" s="4">
-        <v>50.0</v>
+        <v>54.0</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>13</v>
@@ -1439,7 +1442,7 @@
         <v>89</v>
       </c>
       <c r="C27" s="3">
-        <v>10.28</v>
+        <v>10.08</v>
       </c>
       <c r="D27" s="3">
         <v>23.49</v>
@@ -1448,16 +1451,16 @@
         <v>9.75</v>
       </c>
       <c r="F27" s="2">
-        <v>88.1</v>
+        <v>85.1</v>
       </c>
       <c r="G27" s="2">
-        <v>14.4</v>
+        <v>13.9</v>
       </c>
       <c r="H27" s="3">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="I27" s="4">
-        <v>29.0</v>
+        <v>21.0</v>
       </c>
       <c r="K27" s="2" t="s">
         <v>90</v>
@@ -1471,7 +1474,7 @@
         <v>92</v>
       </c>
       <c r="C28" s="3">
-        <v>8.89</v>
+        <v>9.34</v>
       </c>
       <c r="D28" s="3">
         <v>10.55</v>
@@ -1480,16 +1483,16 @@
         <v>6.12</v>
       </c>
       <c r="F28" s="2">
-        <v>332.1</v>
+        <v>339.9</v>
       </c>
       <c r="G28" s="2">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="H28" s="3">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="I28" s="4">
-        <v>42.0</v>
+        <v>46.0</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>13</v>
@@ -1506,7 +1509,7 @@
         <v>95</v>
       </c>
       <c r="C29" s="3">
-        <v>24.1</v>
+        <v>24.61</v>
       </c>
       <c r="D29" s="3">
         <v>29.91</v>
@@ -1515,16 +1518,16 @@
         <v>17.61</v>
       </c>
       <c r="F29" s="2">
-        <v>146.9</v>
+        <v>144.7</v>
       </c>
       <c r="G29" s="2">
-        <v>18.4</v>
+        <v>18.1</v>
       </c>
       <c r="H29" s="3">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="I29" s="4">
-        <v>75.0</v>
+        <v>72.0</v>
       </c>
       <c r="K29" s="2" t="s">
         <v>96</v>
@@ -1538,16 +1541,16 @@
         <v>98</v>
       </c>
       <c r="C30" s="3">
-        <v>14.5</v>
+        <v>14.82</v>
       </c>
       <c r="D30" s="3">
-        <v>28.97</v>
+        <v>27.95</v>
       </c>
       <c r="E30" s="3">
         <v>12.57</v>
       </c>
       <c r="F30" s="2">
-        <v>263.5</v>
+        <v>265.5</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>23</v>
@@ -1556,7 +1559,7 @@
         <v>0.5</v>
       </c>
       <c r="I30" s="4">
-        <v>27.0</v>
+        <v>29.0</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>

--- a/AAII.xlsx
+++ b/AAII.xlsx
@@ -9,14 +9,14 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="lWQN1s3ZBhtXq72gqecZAxt6/OFVzTKZDPKYqIk6YC4="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="f/n/31W9Z+Q9gnWk5OD/iA8Mw1lkIu6giPZPFJGC2xA="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="100">
   <si>
     <t>Company</t>
   </si>
@@ -624,7 +624,7 @@
         <v>12</v>
       </c>
       <c r="C2" s="3">
-        <v>5.09</v>
+        <v>5.84</v>
       </c>
       <c r="D2" s="3">
         <v>7.5</v>
@@ -633,16 +633,16 @@
         <v>4.34</v>
       </c>
       <c r="F2" s="2">
-        <v>51.7</v>
+        <v>61.2</v>
       </c>
       <c r="G2" s="2">
-        <v>13.0</v>
+        <v>15.4</v>
       </c>
       <c r="H2" s="3">
-        <v>0.79</v>
+        <v>0.94</v>
       </c>
       <c r="I2" s="4">
-        <v>59.0</v>
+        <v>83.0</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>13</v>
@@ -659,7 +659,7 @@
         <v>16</v>
       </c>
       <c r="C3" s="3">
-        <v>4.36</v>
+        <v>4.46</v>
       </c>
       <c r="D3" s="3">
         <v>6.79</v>
@@ -668,16 +668,16 @@
         <v>3.65</v>
       </c>
       <c r="F3" s="2">
-        <v>181.6</v>
+        <v>189.9</v>
       </c>
       <c r="G3" s="2">
-        <v>8.9</v>
+        <v>9.3</v>
       </c>
       <c r="H3" s="3">
-        <v>0.41</v>
+        <v>0.43</v>
       </c>
       <c r="I3" s="4">
-        <v>20.0</v>
+        <v>27.0</v>
       </c>
       <c r="K3" s="2" t="s">
         <v>17</v>
@@ -691,7 +691,7 @@
         <v>19</v>
       </c>
       <c r="C4" s="3">
-        <v>2.0</v>
+        <v>1.7</v>
       </c>
       <c r="D4" s="3">
         <v>2.66</v>
@@ -700,7 +700,7 @@
         <v>1.66</v>
       </c>
       <c r="F4" s="2">
-        <v>19.5</v>
+        <v>18.6</v>
       </c>
       <c r="G4" s="2">
         <v>1.5</v>
@@ -709,7 +709,7 @@
         <v>0.03</v>
       </c>
       <c r="I4" s="4">
-        <v>64.0</v>
+        <v>68.0</v>
       </c>
       <c r="K4" s="2" t="s">
         <v>20</v>
@@ -723,7 +723,7 @@
         <v>22</v>
       </c>
       <c r="C5" s="3">
-        <v>16.74</v>
+        <v>15.99</v>
       </c>
       <c r="D5" s="3">
         <v>24.4</v>
@@ -732,7 +732,7 @@
         <v>11.99</v>
       </c>
       <c r="F5" s="2">
-        <v>454.8</v>
+        <v>456.1</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>23</v>
@@ -741,7 +741,7 @@
         <v>0.81</v>
       </c>
       <c r="I5" s="4">
-        <v>64.0</v>
+        <v>58.0</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -758,7 +758,7 @@
         <v>27</v>
       </c>
       <c r="C6" s="3">
-        <v>23.02</v>
+        <v>23.27</v>
       </c>
       <c r="D6" s="3">
         <v>28.69</v>
@@ -767,7 +767,7 @@
         <v>16.6</v>
       </c>
       <c r="F6" s="2">
-        <v>196.5</v>
+        <v>197.0</v>
       </c>
       <c r="G6" s="2">
         <v>27.4</v>
@@ -776,7 +776,7 @@
         <v>1.18</v>
       </c>
       <c r="I6" s="4">
-        <v>53.0</v>
+        <v>52.0</v>
       </c>
       <c r="K6" s="2" t="s">
         <v>28</v>
@@ -790,7 +790,7 @@
         <v>30</v>
       </c>
       <c r="C7" s="3">
-        <v>33.76</v>
+        <v>31.95</v>
       </c>
       <c r="D7" s="3">
         <v>49.88</v>
@@ -799,16 +799,16 @@
         <v>18.0</v>
       </c>
       <c r="F7" s="2">
-        <v>839.5</v>
+        <v>830.1</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>23</v>
       </c>
       <c r="H7" s="3">
-        <v>2.03</v>
+        <v>2.01</v>
       </c>
       <c r="I7" s="4">
-        <v>73.0</v>
+        <v>71.0</v>
       </c>
       <c r="K7" s="2" t="s">
         <v>31</v>
@@ -822,7 +822,7 @@
         <v>33</v>
       </c>
       <c r="C8" s="3">
-        <v>22.56</v>
+        <v>22.12</v>
       </c>
       <c r="D8" s="3">
         <v>22.94</v>
@@ -831,16 +831,16 @@
         <v>16.3</v>
       </c>
       <c r="F8" s="2">
-        <v>570.5</v>
+        <v>576.0</v>
       </c>
       <c r="G8" s="2">
-        <v>13.5</v>
+        <v>14.9</v>
       </c>
       <c r="H8" s="3">
         <v>1.83</v>
       </c>
       <c r="I8" s="4">
-        <v>55.0</v>
+        <v>56.0</v>
       </c>
       <c r="K8" s="2" t="s">
         <v>34</v>
@@ -854,7 +854,7 @@
         <v>36</v>
       </c>
       <c r="C9" s="3">
-        <v>19.26</v>
+        <v>18.64</v>
       </c>
       <c r="D9" s="3">
         <v>23.07</v>
@@ -863,16 +863,16 @@
         <v>11.41</v>
       </c>
       <c r="F9" s="2">
-        <v>263.5</v>
+        <v>258.5</v>
       </c>
       <c r="G9" s="2">
-        <v>11.5</v>
+        <v>11.2</v>
       </c>
       <c r="H9" s="3">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="I9" s="4">
-        <v>57.0</v>
+        <v>64.0</v>
       </c>
       <c r="K9" s="2" t="s">
         <v>37</v>
@@ -886,7 +886,7 @@
         <v>39</v>
       </c>
       <c r="C10" s="3">
-        <v>72.42</v>
+        <v>71.24</v>
       </c>
       <c r="D10" s="3">
         <v>79.67</v>
@@ -895,16 +895,16 @@
         <v>51.0</v>
       </c>
       <c r="F10" s="2">
-        <v>497.5</v>
+        <v>518.0</v>
       </c>
       <c r="G10" s="2">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="H10" s="3">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="I10" s="4">
-        <v>56.0</v>
+        <v>68.0</v>
       </c>
       <c r="K10" s="2" t="s">
         <v>40</v>
@@ -918,7 +918,7 @@
         <v>42</v>
       </c>
       <c r="C11" s="3">
-        <v>41.08</v>
+        <v>41.98</v>
       </c>
       <c r="D11" s="3">
         <v>48.77</v>
@@ -927,16 +927,16 @@
         <v>16.55</v>
       </c>
       <c r="F11" s="2">
-        <v>285.8</v>
+        <v>301.9</v>
       </c>
       <c r="G11" s="2">
-        <v>10.3</v>
+        <v>10.9</v>
       </c>
       <c r="H11" s="3">
-        <v>1.74</v>
+        <v>1.84</v>
       </c>
       <c r="I11" s="4">
-        <v>97.0</v>
+        <v>98.0</v>
       </c>
       <c r="K11" s="2" t="s">
         <v>43</v>
@@ -950,25 +950,25 @@
         <v>45</v>
       </c>
       <c r="C12" s="3">
-        <v>10.03</v>
+        <v>8.94</v>
       </c>
       <c r="D12" s="3">
         <v>20.93</v>
       </c>
       <c r="E12" s="3">
-        <v>9.37</v>
+        <v>8.74</v>
       </c>
       <c r="F12" s="2">
-        <v>758.0</v>
+        <v>717.9</v>
       </c>
       <c r="G12" s="2">
-        <v>23.4</v>
+        <v>22.1</v>
       </c>
       <c r="H12" s="3">
-        <v>1.39</v>
+        <v>1.32</v>
       </c>
       <c r="I12" s="4">
-        <v>13.0</v>
+        <v>10.0</v>
       </c>
       <c r="K12" s="2" t="s">
         <v>46</v>
@@ -982,25 +982,25 @@
         <v>48</v>
       </c>
       <c r="C13" s="3">
-        <v>5.23</v>
+        <v>5.14</v>
       </c>
       <c r="D13" s="3">
-        <v>9.75</v>
+        <v>9.65</v>
       </c>
       <c r="E13" s="3">
         <v>4.64</v>
       </c>
       <c r="F13" s="2">
-        <v>221.0</v>
+        <v>217.6</v>
       </c>
       <c r="G13" s="2">
-        <v>25.2</v>
+        <v>24.9</v>
       </c>
       <c r="H13" s="3">
-        <v>0.91</v>
+        <v>0.89</v>
       </c>
       <c r="I13" s="4">
-        <v>37.0</v>
+        <v>32.0</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>13</v>
@@ -1020,19 +1020,19 @@
         <v>6.15</v>
       </c>
       <c r="D14" s="3">
-        <v>5.97</v>
+        <v>6.19</v>
       </c>
       <c r="E14" s="3">
         <v>2.85</v>
       </c>
       <c r="F14" s="2">
-        <v>74.0</v>
+        <v>76.5</v>
       </c>
       <c r="G14" s="2">
-        <v>15.8</v>
+        <v>16.4</v>
       </c>
       <c r="H14" s="3">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="I14" s="4">
         <v>96.0</v>
@@ -1046,7 +1046,7 @@
         <v>53</v>
       </c>
       <c r="C15" s="3">
-        <v>28.79</v>
+        <v>28.68</v>
       </c>
       <c r="D15" s="3">
         <v>32.0</v>
@@ -1055,16 +1055,16 @@
         <v>21.01</v>
       </c>
       <c r="F15" s="2">
-        <v>678.5</v>
+        <v>690.0</v>
       </c>
       <c r="G15" s="2">
-        <v>25.1</v>
+        <v>25.5</v>
       </c>
       <c r="H15" s="3">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="I15" s="4">
-        <v>73.0</v>
+        <v>70.0</v>
       </c>
       <c r="K15" s="2" t="s">
         <v>54</v>
@@ -1078,7 +1078,7 @@
         <v>56</v>
       </c>
       <c r="C16" s="3">
-        <v>6.16</v>
+        <v>6.45</v>
       </c>
       <c r="D16" s="3">
         <v>6.94</v>
@@ -1087,19 +1087,16 @@
         <v>3.35</v>
       </c>
       <c r="F16" s="2">
-        <v>219.2</v>
+        <v>232.4</v>
       </c>
       <c r="G16" s="2">
-        <v>11.4</v>
+        <v>12.0</v>
       </c>
       <c r="H16" s="3">
-        <v>1.0</v>
+        <v>1.06</v>
       </c>
       <c r="I16" s="4">
-        <v>74.0</v>
-      </c>
-      <c r="J16" s="2" t="s">
-        <v>13</v>
+        <v>83.0</v>
       </c>
       <c r="K16" s="2" t="s">
         <v>57</v>
@@ -1113,7 +1110,7 @@
         <v>59</v>
       </c>
       <c r="C17" s="3">
-        <v>7.15</v>
+        <v>6.73</v>
       </c>
       <c r="D17" s="3">
         <v>8.37</v>
@@ -1122,16 +1119,16 @@
         <v>5.5</v>
       </c>
       <c r="F17" s="2">
-        <v>87.3</v>
+        <v>80.0</v>
       </c>
       <c r="G17" s="2">
-        <v>43.5</v>
+        <v>39.9</v>
       </c>
       <c r="H17" s="3">
-        <v>0.95</v>
+        <v>0.87</v>
       </c>
       <c r="I17" s="4">
-        <v>79.0</v>
+        <v>70.0</v>
       </c>
       <c r="K17" s="2" t="s">
         <v>60</v>
@@ -1145,7 +1142,7 @@
         <v>62</v>
       </c>
       <c r="C18" s="3">
-        <v>20.65</v>
+        <v>20.77</v>
       </c>
       <c r="D18" s="3">
         <v>21.77</v>
@@ -1154,16 +1151,16 @@
         <v>9.37</v>
       </c>
       <c r="F18" s="2">
-        <v>657.1</v>
+        <v>659.3</v>
       </c>
       <c r="G18" s="2">
-        <v>25.1</v>
+        <v>25.2</v>
       </c>
       <c r="H18" s="3">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="I18" s="4">
-        <v>84.0</v>
+        <v>79.0</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>63</v>
@@ -1180,7 +1177,7 @@
         <v>66</v>
       </c>
       <c r="C19" s="3">
-        <v>36.25</v>
+        <v>35.57</v>
       </c>
       <c r="D19" s="3">
         <v>59.42</v>
@@ -1189,16 +1186,16 @@
         <v>35.45</v>
       </c>
       <c r="F19" s="2">
-        <v>274.5</v>
+        <v>275.7</v>
       </c>
       <c r="G19" s="2">
-        <v>15.9</v>
+        <v>16.0</v>
       </c>
       <c r="H19" s="3">
         <v>0.63</v>
       </c>
       <c r="I19" s="4">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="K19" s="2" t="s">
         <v>67</v>
@@ -1212,7 +1209,7 @@
         <v>69</v>
       </c>
       <c r="C20" s="3">
-        <v>33.17</v>
+        <v>33.1</v>
       </c>
       <c r="D20" s="3">
         <v>44.61</v>
@@ -1221,16 +1218,16 @@
         <v>25.53</v>
       </c>
       <c r="F20" s="2">
-        <v>422.4</v>
+        <v>428.0</v>
       </c>
       <c r="G20" s="2">
-        <v>20.5</v>
+        <v>20.7</v>
       </c>
       <c r="H20" s="3">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="I20" s="4">
-        <v>34.0</v>
+        <v>36.0</v>
       </c>
       <c r="K20" s="2" t="s">
         <v>70</v>
@@ -1244,7 +1241,7 @@
         <v>72</v>
       </c>
       <c r="C21" s="3">
-        <v>8.23</v>
+        <v>8.17</v>
       </c>
       <c r="D21" s="3">
         <v>14.5</v>
@@ -1253,7 +1250,7 @@
         <v>5.5</v>
       </c>
       <c r="F21" s="2">
-        <v>494.0</v>
+        <v>494.6</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>23</v>
@@ -1279,7 +1276,7 @@
         <v>75</v>
       </c>
       <c r="C22" s="3">
-        <v>8.43</v>
+        <v>8.32</v>
       </c>
       <c r="D22" s="3">
         <v>9.39</v>
@@ -1288,16 +1285,16 @@
         <v>4.54</v>
       </c>
       <c r="F22" s="2">
-        <v>550.6</v>
+        <v>563.1</v>
       </c>
       <c r="G22" s="2">
-        <v>11.6</v>
+        <v>11.9</v>
       </c>
       <c r="H22" s="3">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="I22" s="4">
-        <v>71.0</v>
+        <v>73.0</v>
       </c>
       <c r="K22" s="2" t="s">
         <v>76</v>
@@ -1311,7 +1308,7 @@
         <v>78</v>
       </c>
       <c r="C23" s="3">
-        <v>47.37</v>
+        <v>49.03</v>
       </c>
       <c r="D23" s="3">
         <v>53.3</v>
@@ -1320,16 +1317,16 @@
         <v>18.06</v>
       </c>
       <c r="F23" s="2">
-        <v>651.8</v>
+        <v>678.5</v>
       </c>
       <c r="G23" s="2">
-        <v>24.0</v>
+        <v>25.0</v>
       </c>
       <c r="H23" s="3">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="I23" s="4">
-        <v>96.0</v>
+        <v>95.0</v>
       </c>
       <c r="K23" s="2" t="s">
         <v>79</v>
@@ -1343,7 +1340,7 @@
         <v>81</v>
       </c>
       <c r="C24" s="3">
-        <v>29.05</v>
+        <v>29.45</v>
       </c>
       <c r="D24" s="3">
         <v>31.5</v>
@@ -1361,7 +1358,7 @@
         <v>0.38</v>
       </c>
       <c r="I24" s="4">
-        <v>73.0</v>
+        <v>77.0</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>13</v>
@@ -1378,7 +1375,7 @@
         <v>84</v>
       </c>
       <c r="C25" s="3">
-        <v>46.74</v>
+        <v>44.93</v>
       </c>
       <c r="D25" s="3">
         <v>53.01</v>
@@ -1387,16 +1384,16 @@
         <v>26.29</v>
       </c>
       <c r="F25" s="2">
-        <v>344.6</v>
+        <v>340.3</v>
       </c>
       <c r="G25" s="2">
-        <v>12.1</v>
+        <v>11.9</v>
       </c>
       <c r="H25" s="3">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="I25" s="4">
-        <v>73.0</v>
+        <v>60.0</v>
       </c>
       <c r="K25" s="2" t="s">
         <v>85</v>
@@ -1410,7 +1407,7 @@
         <v>87</v>
       </c>
       <c r="C26" s="3">
-        <v>5.34</v>
+        <v>5.28</v>
       </c>
       <c r="D26" s="3">
         <v>5.92</v>
@@ -1419,16 +1416,16 @@
         <v>2.03</v>
       </c>
       <c r="F26" s="2">
-        <v>218.8</v>
+        <v>224.7</v>
       </c>
       <c r="G26" s="2">
-        <v>20.7</v>
+        <v>21.3</v>
       </c>
       <c r="H26" s="3">
-        <v>0.84</v>
+        <v>0.87</v>
       </c>
       <c r="I26" s="4">
-        <v>54.0</v>
+        <v>66.0</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>13</v>
@@ -1442,7 +1439,7 @@
         <v>89</v>
       </c>
       <c r="C27" s="3">
-        <v>10.08</v>
+        <v>10.15</v>
       </c>
       <c r="D27" s="3">
         <v>23.49</v>
@@ -1451,16 +1448,16 @@
         <v>9.75</v>
       </c>
       <c r="F27" s="2">
-        <v>85.1</v>
+        <v>85.7</v>
       </c>
       <c r="G27" s="2">
-        <v>13.9</v>
+        <v>14.0</v>
       </c>
       <c r="H27" s="3">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="I27" s="4">
-        <v>21.0</v>
+        <v>18.0</v>
       </c>
       <c r="K27" s="2" t="s">
         <v>90</v>
@@ -1474,7 +1471,7 @@
         <v>92</v>
       </c>
       <c r="C28" s="3">
-        <v>9.34</v>
+        <v>9.05</v>
       </c>
       <c r="D28" s="3">
         <v>10.55</v>
@@ -1483,16 +1480,16 @@
         <v>6.12</v>
       </c>
       <c r="F28" s="2">
-        <v>339.9</v>
+        <v>342.9</v>
       </c>
       <c r="G28" s="2">
         <v>5.6</v>
       </c>
       <c r="H28" s="3">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="I28" s="4">
-        <v>46.0</v>
+        <v>50.0</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>13</v>
@@ -1509,7 +1506,7 @@
         <v>95</v>
       </c>
       <c r="C29" s="3">
-        <v>24.61</v>
+        <v>24.59</v>
       </c>
       <c r="D29" s="3">
         <v>29.91</v>
@@ -1518,16 +1515,16 @@
         <v>17.61</v>
       </c>
       <c r="F29" s="2">
-        <v>144.7</v>
+        <v>151.3</v>
       </c>
       <c r="G29" s="2">
-        <v>18.1</v>
+        <v>19.0</v>
       </c>
       <c r="H29" s="3">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="I29" s="4">
-        <v>72.0</v>
+        <v>73.0</v>
       </c>
       <c r="K29" s="2" t="s">
         <v>96</v>
@@ -1541,25 +1538,25 @@
         <v>98</v>
       </c>
       <c r="C30" s="3">
-        <v>14.82</v>
+        <v>14.66</v>
       </c>
       <c r="D30" s="3">
-        <v>27.95</v>
+        <v>26.56</v>
       </c>
       <c r="E30" s="3">
         <v>12.57</v>
       </c>
       <c r="F30" s="2">
-        <v>265.5</v>
+        <v>270.9</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>23</v>
       </c>
       <c r="H30" s="3">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="I30" s="4">
-        <v>29.0</v>
+        <v>28.0</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>

--- a/AAII.xlsx
+++ b/AAII.xlsx
@@ -9,7 +9,7 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="f/n/31W9Z+Q9gnWk5OD/iA8Mw1lkIu6giPZPFJGC2xA="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="8zEqa7LOUDSYkPs4cjLD7dljM8fGCSbpwe2aK3fC7R0="/>
     </ext>
   </extLst>
 </workbook>
@@ -168,10 +168,10 @@
     <t>News Archive for HDSN</t>
   </si>
   <si>
-    <t>Jerash Holdings (US), Inc. *</t>
-  </si>
-  <si>
-    <t>JRSH*</t>
+    <t>Jerash Holdings (US), Inc.</t>
+  </si>
+  <si>
+    <t>JRSH</t>
   </si>
   <si>
     <t>Kimball Electronics, Inc.</t>
@@ -276,10 +276,10 @@
     <t>News Archive for RCKY</t>
   </si>
   <si>
-    <t>Smart Sand, Inc. *</t>
-  </si>
-  <si>
-    <t>SND*</t>
+    <t>Smart Sand, Inc.</t>
+  </si>
+  <si>
+    <t>SND</t>
   </si>
   <si>
     <t>Smith Douglas Homes Corp.</t>
@@ -624,7 +624,7 @@
         <v>12</v>
       </c>
       <c r="C2" s="3">
-        <v>5.84</v>
+        <v>5.55</v>
       </c>
       <c r="D2" s="3">
         <v>7.5</v>
@@ -633,16 +633,16 @@
         <v>4.34</v>
       </c>
       <c r="F2" s="2">
-        <v>61.2</v>
+        <v>58.4</v>
       </c>
       <c r="G2" s="2">
-        <v>15.4</v>
+        <v>14.7</v>
       </c>
       <c r="H2" s="3">
-        <v>0.94</v>
+        <v>0.89</v>
       </c>
       <c r="I2" s="4">
-        <v>83.0</v>
+        <v>82.0</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>13</v>
@@ -659,7 +659,7 @@
         <v>16</v>
       </c>
       <c r="C3" s="3">
-        <v>4.46</v>
+        <v>4.43</v>
       </c>
       <c r="D3" s="3">
         <v>6.79</v>
@@ -668,16 +668,16 @@
         <v>3.65</v>
       </c>
       <c r="F3" s="2">
-        <v>189.9</v>
+        <v>180.3</v>
       </c>
       <c r="G3" s="2">
-        <v>9.3</v>
+        <v>8.8</v>
       </c>
       <c r="H3" s="3">
-        <v>0.43</v>
+        <v>0.41</v>
       </c>
       <c r="I3" s="4">
-        <v>27.0</v>
+        <v>30.0</v>
       </c>
       <c r="K3" s="2" t="s">
         <v>17</v>
@@ -691,25 +691,25 @@
         <v>19</v>
       </c>
       <c r="C4" s="3">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="D4" s="3">
         <v>2.66</v>
       </c>
       <c r="E4" s="3">
-        <v>1.66</v>
+        <v>1.57</v>
       </c>
       <c r="F4" s="2">
-        <v>18.6</v>
+        <v>16.0</v>
       </c>
       <c r="G4" s="2">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="H4" s="3">
         <v>0.03</v>
       </c>
       <c r="I4" s="4">
-        <v>68.0</v>
+        <v>44.0</v>
       </c>
       <c r="K4" s="2" t="s">
         <v>20</v>
@@ -723,7 +723,7 @@
         <v>22</v>
       </c>
       <c r="C5" s="3">
-        <v>15.99</v>
+        <v>14.64</v>
       </c>
       <c r="D5" s="3">
         <v>24.4</v>
@@ -732,16 +732,16 @@
         <v>11.99</v>
       </c>
       <c r="F5" s="2">
-        <v>456.1</v>
+        <v>428.4</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>23</v>
       </c>
       <c r="H5" s="3">
-        <v>0.81</v>
+        <v>0.76</v>
       </c>
       <c r="I5" s="4">
-        <v>58.0</v>
+        <v>56.0</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -758,7 +758,7 @@
         <v>27</v>
       </c>
       <c r="C6" s="3">
-        <v>23.27</v>
+        <v>22.91</v>
       </c>
       <c r="D6" s="3">
         <v>28.69</v>
@@ -767,16 +767,16 @@
         <v>16.6</v>
       </c>
       <c r="F6" s="2">
-        <v>197.0</v>
+        <v>200.0</v>
       </c>
       <c r="G6" s="2">
-        <v>27.4</v>
+        <v>27.8</v>
       </c>
       <c r="H6" s="3">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="I6" s="4">
-        <v>52.0</v>
+        <v>41.0</v>
       </c>
       <c r="K6" s="2" t="s">
         <v>28</v>
@@ -790,7 +790,7 @@
         <v>30</v>
       </c>
       <c r="C7" s="3">
-        <v>31.95</v>
+        <v>30.72</v>
       </c>
       <c r="D7" s="3">
         <v>49.88</v>
@@ -799,16 +799,16 @@
         <v>18.0</v>
       </c>
       <c r="F7" s="2">
-        <v>830.1</v>
+        <v>781.9</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>23</v>
       </c>
       <c r="H7" s="3">
-        <v>2.01</v>
+        <v>1.89</v>
       </c>
       <c r="I7" s="4">
-        <v>71.0</v>
+        <v>64.0</v>
       </c>
       <c r="K7" s="2" t="s">
         <v>31</v>
@@ -822,7 +822,7 @@
         <v>33</v>
       </c>
       <c r="C8" s="3">
-        <v>22.12</v>
+        <v>22.36</v>
       </c>
       <c r="D8" s="3">
         <v>22.94</v>
@@ -831,16 +831,16 @@
         <v>16.3</v>
       </c>
       <c r="F8" s="2">
-        <v>576.0</v>
+        <v>567.6</v>
       </c>
       <c r="G8" s="2">
-        <v>14.9</v>
+        <v>14.7</v>
       </c>
       <c r="H8" s="3">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="I8" s="4">
-        <v>56.0</v>
+        <v>64.0</v>
       </c>
       <c r="K8" s="2" t="s">
         <v>34</v>
@@ -854,7 +854,7 @@
         <v>36</v>
       </c>
       <c r="C9" s="3">
-        <v>18.64</v>
+        <v>18.49</v>
       </c>
       <c r="D9" s="3">
         <v>23.07</v>
@@ -863,16 +863,16 @@
         <v>11.41</v>
       </c>
       <c r="F9" s="2">
-        <v>258.5</v>
+        <v>257.4</v>
       </c>
       <c r="G9" s="2">
         <v>11.2</v>
       </c>
       <c r="H9" s="3">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="I9" s="4">
-        <v>64.0</v>
+        <v>61.0</v>
       </c>
       <c r="K9" s="2" t="s">
         <v>37</v>
@@ -886,7 +886,7 @@
         <v>39</v>
       </c>
       <c r="C10" s="3">
-        <v>71.24</v>
+        <v>66.17</v>
       </c>
       <c r="D10" s="3">
         <v>79.67</v>
@@ -895,16 +895,16 @@
         <v>51.0</v>
       </c>
       <c r="F10" s="2">
-        <v>518.0</v>
+        <v>475.9</v>
       </c>
       <c r="G10" s="2">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="H10" s="3">
-        <v>1.06</v>
+        <v>0.92</v>
       </c>
       <c r="I10" s="4">
-        <v>68.0</v>
+        <v>47.0</v>
       </c>
       <c r="K10" s="2" t="s">
         <v>40</v>
@@ -918,7 +918,7 @@
         <v>42</v>
       </c>
       <c r="C11" s="3">
-        <v>41.98</v>
+        <v>40.48</v>
       </c>
       <c r="D11" s="3">
         <v>48.77</v>
@@ -927,13 +927,13 @@
         <v>16.55</v>
       </c>
       <c r="F11" s="2">
-        <v>301.9</v>
+        <v>297.6</v>
       </c>
       <c r="G11" s="2">
-        <v>10.9</v>
+        <v>10.8</v>
       </c>
       <c r="H11" s="3">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="I11" s="4">
         <v>98.0</v>
@@ -950,25 +950,25 @@
         <v>45</v>
       </c>
       <c r="C12" s="3">
-        <v>8.94</v>
+        <v>7.83</v>
       </c>
       <c r="D12" s="3">
         <v>20.93</v>
       </c>
       <c r="E12" s="3">
-        <v>8.74</v>
+        <v>7.77</v>
       </c>
       <c r="F12" s="2">
-        <v>717.9</v>
+        <v>620.1</v>
       </c>
       <c r="G12" s="2">
-        <v>22.1</v>
+        <v>19.1</v>
       </c>
       <c r="H12" s="3">
-        <v>1.32</v>
+        <v>1.14</v>
       </c>
       <c r="I12" s="4">
-        <v>10.0</v>
+        <v>9.0</v>
       </c>
       <c r="K12" s="2" t="s">
         <v>46</v>
@@ -982,7 +982,7 @@
         <v>48</v>
       </c>
       <c r="C13" s="3">
-        <v>5.14</v>
+        <v>5.01</v>
       </c>
       <c r="D13" s="3">
         <v>9.65</v>
@@ -991,16 +991,16 @@
         <v>4.64</v>
       </c>
       <c r="F13" s="2">
-        <v>217.6</v>
+        <v>212.1</v>
       </c>
       <c r="G13" s="2">
-        <v>24.9</v>
+        <v>24.2</v>
       </c>
       <c r="H13" s="3">
-        <v>0.89</v>
+        <v>0.87</v>
       </c>
       <c r="I13" s="4">
-        <v>32.0</v>
+        <v>33.0</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>13</v>
@@ -1017,25 +1017,25 @@
         <v>51</v>
       </c>
       <c r="C14" s="3">
-        <v>6.15</v>
+        <v>6.17</v>
       </c>
       <c r="D14" s="3">
-        <v>6.19</v>
+        <v>6.67</v>
       </c>
       <c r="E14" s="3">
         <v>2.85</v>
       </c>
       <c r="F14" s="2">
-        <v>76.5</v>
+        <v>78.2</v>
       </c>
       <c r="G14" s="2">
-        <v>16.4</v>
+        <v>16.7</v>
       </c>
       <c r="H14" s="3">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="I14" s="4">
-        <v>96.0</v>
+        <v>97.0</v>
       </c>
     </row>
     <row r="15">
@@ -1046,7 +1046,7 @@
         <v>53</v>
       </c>
       <c r="C15" s="3">
-        <v>28.68</v>
+        <v>25.86</v>
       </c>
       <c r="D15" s="3">
         <v>32.0</v>
@@ -1055,16 +1055,16 @@
         <v>21.01</v>
       </c>
       <c r="F15" s="2">
-        <v>690.0</v>
+        <v>635.1</v>
       </c>
       <c r="G15" s="2">
-        <v>25.5</v>
+        <v>23.5</v>
       </c>
       <c r="H15" s="3">
-        <v>1.18</v>
+        <v>1.09</v>
       </c>
       <c r="I15" s="4">
-        <v>70.0</v>
+        <v>57.0</v>
       </c>
       <c r="K15" s="2" t="s">
         <v>54</v>
@@ -1078,7 +1078,7 @@
         <v>56</v>
       </c>
       <c r="C16" s="3">
-        <v>6.45</v>
+        <v>6.97</v>
       </c>
       <c r="D16" s="3">
         <v>6.94</v>
@@ -1087,13 +1087,13 @@
         <v>3.35</v>
       </c>
       <c r="F16" s="2">
-        <v>232.4</v>
+        <v>236.9</v>
       </c>
       <c r="G16" s="2">
-        <v>12.0</v>
+        <v>12.3</v>
       </c>
       <c r="H16" s="3">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="I16" s="4">
         <v>83.0</v>
@@ -1110,7 +1110,7 @@
         <v>59</v>
       </c>
       <c r="C17" s="3">
-        <v>6.73</v>
+        <v>6.35</v>
       </c>
       <c r="D17" s="3">
         <v>8.37</v>
@@ -1119,16 +1119,16 @@
         <v>5.5</v>
       </c>
       <c r="F17" s="2">
-        <v>80.0</v>
+        <v>77.1</v>
       </c>
       <c r="G17" s="2">
-        <v>39.9</v>
+        <v>38.4</v>
       </c>
       <c r="H17" s="3">
-        <v>0.87</v>
+        <v>0.84</v>
       </c>
       <c r="I17" s="4">
-        <v>70.0</v>
+        <v>50.0</v>
       </c>
       <c r="K17" s="2" t="s">
         <v>60</v>
@@ -1142,19 +1142,19 @@
         <v>62</v>
       </c>
       <c r="C18" s="3">
-        <v>20.77</v>
+        <v>21.46</v>
       </c>
       <c r="D18" s="3">
         <v>21.77</v>
       </c>
       <c r="E18" s="3">
-        <v>9.37</v>
+        <v>9.45</v>
       </c>
       <c r="F18" s="2">
-        <v>659.3</v>
+        <v>658.3</v>
       </c>
       <c r="G18" s="2">
-        <v>25.2</v>
+        <v>25.1</v>
       </c>
       <c r="H18" s="3">
         <v>2.75</v>
@@ -1177,25 +1177,25 @@
         <v>66</v>
       </c>
       <c r="C19" s="3">
-        <v>35.57</v>
+        <v>34.28</v>
       </c>
       <c r="D19" s="3">
         <v>59.42</v>
       </c>
       <c r="E19" s="3">
-        <v>35.45</v>
+        <v>33.39</v>
       </c>
       <c r="F19" s="2">
-        <v>275.7</v>
+        <v>253.7</v>
       </c>
       <c r="G19" s="2">
-        <v>16.0</v>
+        <v>14.7</v>
       </c>
       <c r="H19" s="3">
-        <v>0.63</v>
+        <v>0.58</v>
       </c>
       <c r="I19" s="4">
-        <v>19.0</v>
+        <v>23.0</v>
       </c>
       <c r="K19" s="2" t="s">
         <v>67</v>
@@ -1209,25 +1209,25 @@
         <v>69</v>
       </c>
       <c r="C20" s="3">
-        <v>33.1</v>
+        <v>31.1</v>
       </c>
       <c r="D20" s="3">
         <v>44.61</v>
       </c>
       <c r="E20" s="3">
-        <v>25.53</v>
+        <v>25.71</v>
       </c>
       <c r="F20" s="2">
-        <v>428.0</v>
+        <v>399.3</v>
       </c>
       <c r="G20" s="2">
-        <v>20.7</v>
+        <v>19.3</v>
       </c>
       <c r="H20" s="3">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
       <c r="I20" s="4">
-        <v>36.0</v>
+        <v>32.0</v>
       </c>
       <c r="K20" s="2" t="s">
         <v>70</v>
@@ -1241,7 +1241,7 @@
         <v>72</v>
       </c>
       <c r="C21" s="3">
-        <v>8.17</v>
+        <v>8.12</v>
       </c>
       <c r="D21" s="3">
         <v>14.5</v>
@@ -1250,16 +1250,16 @@
         <v>5.5</v>
       </c>
       <c r="F21" s="2">
-        <v>494.6</v>
+        <v>479.0</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>23</v>
       </c>
       <c r="H21" s="3">
-        <v>0.85</v>
+        <v>0.82</v>
       </c>
       <c r="I21" s="4">
-        <v>20.0</v>
+        <v>25.0</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -1276,25 +1276,25 @@
         <v>75</v>
       </c>
       <c r="C22" s="3">
-        <v>8.32</v>
+        <v>7.61</v>
       </c>
       <c r="D22" s="3">
         <v>9.39</v>
       </c>
       <c r="E22" s="3">
-        <v>4.54</v>
+        <v>4.71</v>
       </c>
       <c r="F22" s="2">
-        <v>563.1</v>
+        <v>515.3</v>
       </c>
       <c r="G22" s="2">
-        <v>11.9</v>
+        <v>10.9</v>
       </c>
       <c r="H22" s="3">
-        <v>1.26</v>
+        <v>1.15</v>
       </c>
       <c r="I22" s="4">
-        <v>73.0</v>
+        <v>58.0</v>
       </c>
       <c r="K22" s="2" t="s">
         <v>76</v>
@@ -1308,7 +1308,7 @@
         <v>78</v>
       </c>
       <c r="C23" s="3">
-        <v>49.03</v>
+        <v>45.75</v>
       </c>
       <c r="D23" s="3">
         <v>53.3</v>
@@ -1317,16 +1317,16 @@
         <v>18.06</v>
       </c>
       <c r="F23" s="2">
-        <v>678.5</v>
+        <v>646.9</v>
       </c>
       <c r="G23" s="2">
-        <v>25.0</v>
+        <v>23.8</v>
       </c>
       <c r="H23" s="3">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="I23" s="4">
-        <v>95.0</v>
+        <v>96.0</v>
       </c>
       <c r="K23" s="2" t="s">
         <v>79</v>
@@ -1340,25 +1340,25 @@
         <v>81</v>
       </c>
       <c r="C24" s="3">
-        <v>29.45</v>
+        <v>29.0</v>
       </c>
       <c r="D24" s="3">
-        <v>31.5</v>
+        <v>30.93</v>
       </c>
       <c r="E24" s="3">
         <v>19.31</v>
       </c>
       <c r="F24" s="2">
-        <v>73.5</v>
+        <v>72.9</v>
       </c>
       <c r="G24" s="2">
-        <v>12.2</v>
+        <v>12.1</v>
       </c>
       <c r="H24" s="3">
         <v>0.38</v>
       </c>
       <c r="I24" s="4">
-        <v>77.0</v>
+        <v>72.0</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>13</v>
@@ -1375,25 +1375,25 @@
         <v>84</v>
       </c>
       <c r="C25" s="3">
-        <v>44.93</v>
+        <v>45.81</v>
       </c>
       <c r="D25" s="3">
         <v>53.01</v>
       </c>
       <c r="E25" s="3">
-        <v>26.29</v>
+        <v>26.73</v>
       </c>
       <c r="F25" s="2">
-        <v>340.3</v>
+        <v>349.7</v>
       </c>
       <c r="G25" s="2">
-        <v>11.9</v>
+        <v>12.3</v>
       </c>
       <c r="H25" s="3">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="I25" s="4">
-        <v>60.0</v>
+        <v>71.0</v>
       </c>
       <c r="K25" s="2" t="s">
         <v>85</v>
@@ -1407,7 +1407,7 @@
         <v>87</v>
       </c>
       <c r="C26" s="3">
-        <v>5.28</v>
+        <v>5.07</v>
       </c>
       <c r="D26" s="3">
         <v>5.92</v>
@@ -1416,16 +1416,16 @@
         <v>2.03</v>
       </c>
       <c r="F26" s="2">
-        <v>224.7</v>
+        <v>214.5</v>
       </c>
       <c r="G26" s="2">
-        <v>21.3</v>
+        <v>20.3</v>
       </c>
       <c r="H26" s="3">
-        <v>0.87</v>
+        <v>0.83</v>
       </c>
       <c r="I26" s="4">
-        <v>66.0</v>
+        <v>54.0</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>13</v>
@@ -1439,25 +1439,25 @@
         <v>89</v>
       </c>
       <c r="C27" s="3">
-        <v>10.15</v>
+        <v>10.4</v>
       </c>
       <c r="D27" s="3">
         <v>23.49</v>
       </c>
       <c r="E27" s="3">
-        <v>9.75</v>
+        <v>9.71</v>
       </c>
       <c r="F27" s="2">
-        <v>85.7</v>
+        <v>87.7</v>
       </c>
       <c r="G27" s="2">
-        <v>14.0</v>
+        <v>14.3</v>
       </c>
       <c r="H27" s="3">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="I27" s="4">
-        <v>18.0</v>
+        <v>28.0</v>
       </c>
       <c r="K27" s="2" t="s">
         <v>90</v>
@@ -1471,25 +1471,25 @@
         <v>92</v>
       </c>
       <c r="C28" s="3">
-        <v>9.05</v>
+        <v>8.57</v>
       </c>
       <c r="D28" s="3">
         <v>10.55</v>
       </c>
       <c r="E28" s="3">
-        <v>6.12</v>
+        <v>6.31</v>
       </c>
       <c r="F28" s="2">
-        <v>342.9</v>
+        <v>318.3</v>
       </c>
       <c r="G28" s="2">
-        <v>5.6</v>
+        <v>5.2</v>
       </c>
       <c r="H28" s="3">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="I28" s="4">
-        <v>50.0</v>
+        <v>46.0</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>13</v>
@@ -1506,7 +1506,7 @@
         <v>95</v>
       </c>
       <c r="C29" s="3">
-        <v>24.59</v>
+        <v>24.31</v>
       </c>
       <c r="D29" s="3">
         <v>29.91</v>
@@ -1515,16 +1515,16 @@
         <v>17.61</v>
       </c>
       <c r="F29" s="2">
-        <v>151.3</v>
+        <v>150.7</v>
       </c>
       <c r="G29" s="2">
-        <v>19.0</v>
+        <v>18.9</v>
       </c>
       <c r="H29" s="3">
         <v>1.16</v>
       </c>
       <c r="I29" s="4">
-        <v>73.0</v>
+        <v>74.0</v>
       </c>
       <c r="K29" s="2" t="s">
         <v>96</v>
@@ -1538,25 +1538,25 @@
         <v>98</v>
       </c>
       <c r="C30" s="3">
-        <v>14.66</v>
+        <v>15.54</v>
       </c>
       <c r="D30" s="3">
-        <v>26.56</v>
+        <v>23.59</v>
       </c>
       <c r="E30" s="3">
         <v>12.57</v>
       </c>
       <c r="F30" s="2">
-        <v>270.9</v>
+        <v>284.2</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>23</v>
       </c>
       <c r="H30" s="3">
-        <v>0.51</v>
+        <v>0.54</v>
       </c>
       <c r="I30" s="4">
-        <v>28.0</v>
+        <v>32.0</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>

--- a/AAII.xlsx
+++ b/AAII.xlsx
@@ -288,7 +288,7 @@
         </is>
       </c>
       <c r="C3" s="66">
-        <v>5.55</v>
+        <v>5.56</v>
       </c>
       <c r="D3" s="66">
         <v>7.50</v>
@@ -297,16 +297,16 @@
         <v>4.34</v>
       </c>
       <c t="n" r="F3">
-        <v>56.6</v>
+        <v>55.5</v>
       </c>
       <c t="n" r="G3">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="H3" s="66">
-        <v>0.87</v>
+        <v>0.86</v>
       </c>
       <c r="I3" s="65">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c t="inlineStr" r="J3">
         <is>
@@ -331,7 +331,7 @@
         </is>
       </c>
       <c r="C4" s="66">
-        <v>4.43</v>
+        <v>4.59</v>
       </c>
       <c r="D4" s="66">
         <v>6.79</v>
@@ -349,7 +349,7 @@
         <v>0.42</v>
       </c>
       <c r="I4" s="65">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c t="inlineStr" r="K4">
         <is>
@@ -369,16 +369,16 @@
         </is>
       </c>
       <c r="C5" s="66">
-        <v>1.64</v>
+        <v>1.60</v>
       </c>
       <c r="D5" s="66">
         <v>2.66</v>
       </c>
       <c r="E5" s="66">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c t="n" r="F5">
-        <v>15.8</v>
+        <v>15.5</v>
       </c>
       <c t="n" r="G5">
         <v>1.2</v>
@@ -387,7 +387,7 @@
         <v>0.03</v>
       </c>
       <c r="I5" s="65">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c t="inlineStr" r="K5">
         <is>
@@ -407,7 +407,7 @@
         </is>
       </c>
       <c r="C6" s="66">
-        <v>14.64</v>
+        <v>13.52</v>
       </c>
       <c r="D6" s="66">
         <v>24.40</v>
@@ -416,7 +416,7 @@
         <v>11.99</v>
       </c>
       <c t="n" r="F6">
-        <v>417.8</v>
+        <v>417.0</v>
       </c>
       <c t="inlineStr" r="G6">
         <is>
@@ -424,10 +424,10 @@
         </is>
       </c>
       <c r="H6" s="66">
-        <v>0.74</v>
+        <v>0.70</v>
       </c>
       <c r="I6" s="65">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c t="inlineStr" r="J6">
         <is>
@@ -452,7 +452,7 @@
         </is>
       </c>
       <c r="C7" s="66">
-        <v>22.91</v>
+        <v>23.13</v>
       </c>
       <c r="D7" s="66">
         <v>28.69</v>
@@ -461,16 +461,16 @@
         <v>16.60</v>
       </c>
       <c t="n" r="F7">
-        <v>196.2</v>
+        <v>201.6</v>
       </c>
       <c t="n" r="G7">
-        <v>27.3</v>
+        <v>28.9</v>
       </c>
       <c r="H7" s="66">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="I7" s="65">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c t="inlineStr" r="K7">
         <is>
@@ -490,7 +490,7 @@
         </is>
       </c>
       <c r="C8" s="66">
-        <v>30.72</v>
+        <v>29.19</v>
       </c>
       <c r="D8" s="66">
         <v>49.88</v>
@@ -499,7 +499,7 @@
         <v>18.00</v>
       </c>
       <c t="n" r="F8">
-        <v>779.6</v>
+        <v>755.5</v>
       </c>
       <c t="inlineStr" r="G8">
         <is>
@@ -507,10 +507,10 @@
         </is>
       </c>
       <c r="H8" s="66">
-        <v>1.89</v>
+        <v>1.83</v>
       </c>
       <c r="I8" s="65">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c t="inlineStr" r="K8">
         <is>
@@ -530,25 +530,25 @@
         </is>
       </c>
       <c r="C9" s="66">
-        <v>22.36</v>
+        <v>22.64</v>
       </c>
       <c r="D9" s="66">
-        <v>22.94</v>
+        <v>23.09</v>
       </c>
       <c r="E9" s="66">
         <v>16.30</v>
       </c>
       <c t="n" r="F9">
-        <v>566.1</v>
+        <v>580.3</v>
       </c>
       <c t="n" r="G9">
-        <v>14.6</v>
+        <v>15.0</v>
       </c>
       <c r="H9" s="66">
-        <v>1.80</v>
+        <v>1.84</v>
       </c>
       <c r="I9" s="65">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c t="inlineStr" r="K9">
         <is>
@@ -568,7 +568,7 @@
         </is>
       </c>
       <c r="C10" s="66">
-        <v>18.49</v>
+        <v>18.54</v>
       </c>
       <c r="D10" s="66">
         <v>23.07</v>
@@ -580,13 +580,13 @@
         <v>254.5</v>
       </c>
       <c t="n" r="G10">
-        <v>11.1</v>
+        <v>11.3</v>
       </c>
       <c r="H10" s="66">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="I10" s="65">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c t="inlineStr" r="K10">
         <is>
@@ -606,7 +606,7 @@
         </is>
       </c>
       <c r="C11" s="66">
-        <v>66.17</v>
+        <v>66.66</v>
       </c>
       <c r="D11" s="66">
         <v>79.67</v>
@@ -615,7 +615,7 @@
         <v>51.00</v>
       </c>
       <c t="n" r="F11">
-        <v>466.9</v>
+        <v>485.9</v>
       </c>
       <c t="n" r="G11">
         <v>3.4</v>
@@ -624,7 +624,7 @@
         <v>0.90</v>
       </c>
       <c r="I11" s="65">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c t="inlineStr" r="K11">
         <is>
@@ -644,7 +644,7 @@
         </is>
       </c>
       <c r="C12" s="66">
-        <v>40.48</v>
+        <v>41.83</v>
       </c>
       <c r="D12" s="66">
         <v>48.77</v>
@@ -653,13 +653,13 @@
         <v>16.55</v>
       </c>
       <c t="n" r="F12">
-        <v>292.0</v>
+        <v>303.3</v>
       </c>
       <c t="n" r="G12">
-        <v>10.5</v>
+        <v>10.6</v>
       </c>
       <c r="H12" s="66">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="I12" s="65">
         <v>98</v>
@@ -682,25 +682,25 @@
         </is>
       </c>
       <c r="C13" s="66">
-        <v>7.83</v>
+        <v>7.44</v>
       </c>
       <c r="D13" s="66">
         <v>20.93</v>
       </c>
       <c r="E13" s="66">
-        <v>7.75</v>
+        <v>7.40</v>
       </c>
       <c t="n" r="F13">
-        <v>603.1</v>
+        <v>606.2</v>
       </c>
       <c t="n" r="G13">
-        <v>18.6</v>
+        <v>17.7</v>
       </c>
       <c r="H13" s="66">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="I13" s="65">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c t="inlineStr" r="K13">
         <is>
@@ -720,7 +720,7 @@
         </is>
       </c>
       <c r="C14" s="66">
-        <v>5.01</v>
+        <v>5.37</v>
       </c>
       <c r="D14" s="66">
         <v>9.65</v>
@@ -729,16 +729,16 @@
         <v>4.64</v>
       </c>
       <c t="n" r="F14">
-        <v>210.9</v>
+        <v>227.7</v>
       </c>
       <c t="n" r="G14">
-        <v>24.1</v>
+        <v>25.7</v>
       </c>
       <c r="H14" s="66">
-        <v>0.87</v>
+        <v>0.93</v>
       </c>
       <c r="I14" s="65">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c t="inlineStr" r="J14">
         <is>
@@ -763,7 +763,7 @@
         </is>
       </c>
       <c r="C15" s="66">
-        <v>6.17</v>
+        <v>6.13</v>
       </c>
       <c r="D15" s="66">
         <v>6.67</v>
@@ -772,16 +772,16 @@
         <v>2.85</v>
       </c>
       <c t="n" r="F15">
-        <v>78.4</v>
+        <v>76.9</v>
       </c>
       <c t="n" r="G15">
-        <v>16.8</v>
+        <v>16.5</v>
       </c>
       <c r="H15" s="66">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="I15" s="65">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="16">
@@ -796,7 +796,7 @@
         </is>
       </c>
       <c r="C16" s="66">
-        <v>25.86</v>
+        <v>24.60</v>
       </c>
       <c r="D16" s="66">
         <v>32.00</v>
@@ -805,16 +805,16 @@
         <v>21.01</v>
       </c>
       <c t="n" r="F16">
-        <v>619.8</v>
+        <v>634.6</v>
       </c>
       <c t="n" r="G16">
-        <v>22.9</v>
+        <v>22.1</v>
       </c>
       <c r="H16" s="66">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="I16" s="65">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c t="inlineStr" r="K16">
         <is>
@@ -834,25 +834,25 @@
         </is>
       </c>
       <c r="C17" s="66">
-        <v>6.97</v>
+        <v>7.28</v>
       </c>
       <c r="D17" s="66">
-        <v>7.03</v>
+        <v>7.13</v>
       </c>
       <c r="E17" s="66">
         <v>3.35</v>
       </c>
       <c t="n" r="F17">
-        <v>249.8</v>
+        <v>252.1</v>
       </c>
       <c t="n" r="G17">
-        <v>12.9</v>
+        <v>12.8</v>
       </c>
       <c r="H17" s="66">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="I17" s="65">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c t="inlineStr" r="K17">
         <is>
@@ -872,7 +872,7 @@
         </is>
       </c>
       <c r="C18" s="66">
-        <v>6.35</v>
+        <v>6.36</v>
       </c>
       <c r="D18" s="66">
         <v>8.37</v>
@@ -881,10 +881,10 @@
         <v>5.50</v>
       </c>
       <c t="n" r="F18">
-        <v>76.3</v>
+        <v>76.9</v>
       </c>
       <c t="n" r="G18">
-        <v>38.0</v>
+        <v>37.7</v>
       </c>
       <c r="H18" s="66">
         <v>0.83</v>
@@ -910,25 +910,25 @@
         </is>
       </c>
       <c r="C19" s="66">
-        <v>21.46</v>
+        <v>21.53</v>
       </c>
       <c r="D19" s="66">
-        <v>21.77</v>
+        <v>21.92</v>
       </c>
       <c r="E19" s="66">
         <v>9.45</v>
       </c>
       <c t="n" r="F19">
-        <v>683.5</v>
+        <v>682.2</v>
       </c>
       <c t="n" r="G19">
         <v>26.1</v>
       </c>
       <c r="H19" s="66">
-        <v>2.85</v>
+        <v>2.84</v>
       </c>
       <c r="I19" s="65">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c t="inlineStr" r="J19">
         <is>
@@ -953,25 +953,25 @@
         </is>
       </c>
       <c r="C20" s="66">
-        <v>34.28</v>
+        <v>34.52</v>
       </c>
       <c r="D20" s="66">
         <v>59.42</v>
       </c>
       <c r="E20" s="66">
-        <v>33.39</v>
+        <v>32.32</v>
       </c>
       <c t="n" r="F20">
-        <v>258.7</v>
+        <v>252.5</v>
       </c>
       <c t="n" r="G20">
-        <v>15.0</v>
+        <v>14.6</v>
       </c>
       <c r="H20" s="66">
-        <v>0.59</v>
+        <v>0.58</v>
       </c>
       <c r="I20" s="65">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c t="inlineStr" r="K20">
         <is>
@@ -991,25 +991,25 @@
         </is>
       </c>
       <c r="C21" s="66">
-        <v>31.10</v>
+        <v>30.97</v>
       </c>
       <c r="D21" s="66">
         <v>44.61</v>
       </c>
       <c r="E21" s="66">
-        <v>25.72</v>
+        <v>27.05</v>
       </c>
       <c t="n" r="F21">
-        <v>401.1</v>
+        <v>387.5</v>
       </c>
       <c t="n" r="G21">
-        <v>19.4</v>
+        <v>18.8</v>
       </c>
       <c r="H21" s="66">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="I21" s="65">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c t="inlineStr" r="K21">
         <is>
@@ -1029,7 +1029,7 @@
         </is>
       </c>
       <c r="C22" s="66">
-        <v>8.12</v>
+        <v>8.60</v>
       </c>
       <c r="D22" s="66">
         <v>14.50</v>
@@ -1038,7 +1038,7 @@
         <v>5.50</v>
       </c>
       <c t="n" r="F22">
-        <v>489.8</v>
+        <v>485.0</v>
       </c>
       <c t="inlineStr" r="G22">
         <is>
@@ -1046,10 +1046,10 @@
         </is>
       </c>
       <c r="H22" s="66">
-        <v>0.84</v>
+        <v>0.83</v>
       </c>
       <c r="I22" s="65">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c t="inlineStr" r="J22">
         <is>
@@ -1074,7 +1074,7 @@
         </is>
       </c>
       <c r="C23" s="66">
-        <v>7.62</v>
+        <v>7.94</v>
       </c>
       <c r="D23" s="66">
         <v>9.39</v>
@@ -1083,16 +1083,16 @@
         <v>4.71</v>
       </c>
       <c t="n" r="F23">
-        <v>498.9</v>
+        <v>509.4</v>
       </c>
       <c t="n" r="G23">
-        <v>10.5</v>
+        <v>10.7</v>
       </c>
       <c r="H23" s="66">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="I23" s="65">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c t="inlineStr" r="K23">
         <is>
@@ -1112,7 +1112,7 @@
         </is>
       </c>
       <c r="C24" s="66">
-        <v>45.75</v>
+        <v>42.86</v>
       </c>
       <c r="D24" s="66">
         <v>53.30</v>
@@ -1121,16 +1121,16 @@
         <v>18.06</v>
       </c>
       <c t="n" r="F24">
-        <v>640.7</v>
+        <v>648.7</v>
       </c>
       <c t="n" r="G24">
-        <v>23.6</v>
+        <v>22.3</v>
       </c>
       <c r="H24" s="66">
-        <v>1.64</v>
+        <v>1.55</v>
       </c>
       <c r="I24" s="65">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c t="inlineStr" r="K24">
         <is>
@@ -1150,7 +1150,7 @@
         </is>
       </c>
       <c r="C25" s="66">
-        <v>29.00</v>
+        <v>29.40</v>
       </c>
       <c r="D25" s="66">
         <v>30.93</v>
@@ -1159,16 +1159,16 @@
         <v>19.31</v>
       </c>
       <c t="n" r="F25">
-        <v>72.5</v>
+        <v>73.8</v>
       </c>
       <c t="n" r="G25">
-        <v>12.0</v>
+        <v>12.2</v>
       </c>
       <c r="H25" s="66">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="I25" s="65">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c t="inlineStr" r="J25">
         <is>
@@ -1193,25 +1193,25 @@
         </is>
       </c>
       <c r="C26" s="66">
-        <v>45.81</v>
+        <v>46.84</v>
       </c>
       <c r="D26" s="66">
         <v>53.01</v>
       </c>
       <c r="E26" s="66">
-        <v>26.90</v>
+        <v>27.22</v>
       </c>
       <c t="n" r="F26">
-        <v>343.2</v>
+        <v>346.8</v>
       </c>
       <c t="n" r="G26">
-        <v>12.0</v>
+        <v>12.5</v>
       </c>
       <c r="H26" s="66">
-        <v>1.30</v>
+        <v>1.35</v>
       </c>
       <c r="I26" s="65">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c t="inlineStr" r="K26">
         <is>
@@ -1231,25 +1231,25 @@
         </is>
       </c>
       <c r="C27" s="66">
-        <v>5.08</v>
+        <v>4.76</v>
       </c>
       <c r="D27" s="66">
         <v>5.92</v>
       </c>
       <c r="E27" s="66">
-        <v>2.03</v>
+        <v>2.08</v>
       </c>
       <c t="n" r="F27">
-        <v>215.2</v>
+        <v>201.4</v>
       </c>
       <c t="n" r="G27">
-        <v>20.4</v>
+        <v>19.1</v>
       </c>
       <c r="H27" s="66">
-        <v>0.83</v>
+        <v>0.78</v>
       </c>
       <c r="I27" s="65">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c t="inlineStr" r="J27">
         <is>
@@ -1269,7 +1269,7 @@
         </is>
       </c>
       <c r="C28" s="66">
-        <v>10.40</v>
+        <v>10.44</v>
       </c>
       <c r="D28" s="66">
         <v>23.49</v>
@@ -1278,16 +1278,16 @@
         <v>9.71</v>
       </c>
       <c t="n" r="F28">
-        <v>87.3</v>
+        <v>85.1</v>
       </c>
       <c t="n" r="G28">
-        <v>14.2</v>
+        <v>13.9</v>
       </c>
       <c r="H28" s="66">
-        <v>1.10</v>
+        <v>1.07</v>
       </c>
       <c r="I28" s="65">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c t="inlineStr" r="K28">
         <is>
@@ -1307,25 +1307,25 @@
         </is>
       </c>
       <c r="C29" s="66">
-        <v>8.57</v>
+        <v>8.26</v>
       </c>
       <c r="D29" s="66">
         <v>10.55</v>
       </c>
       <c r="E29" s="66">
-        <v>6.31</v>
+        <v>6.46</v>
       </c>
       <c t="n" r="F29">
-        <v>318.7</v>
+        <v>307.9</v>
       </c>
       <c t="n" r="G29">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="H29" s="66">
-        <v>0.46</v>
+        <v>0.44</v>
       </c>
       <c r="I29" s="65">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c t="inlineStr" r="J29">
         <is>
@@ -1350,7 +1350,7 @@
         </is>
       </c>
       <c r="C30" s="66">
-        <v>24.31</v>
+        <v>24.18</v>
       </c>
       <c r="D30" s="66">
         <v>29.91</v>
@@ -1362,13 +1362,13 @@
         <v>146.3</v>
       </c>
       <c t="n" r="G30">
-        <v>18.3</v>
+        <v>18.7</v>
       </c>
       <c r="H30" s="66">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="I30" s="65">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c t="inlineStr" r="K30">
         <is>
@@ -1388,7 +1388,7 @@
         </is>
       </c>
       <c r="C31" s="66">
-        <v>15.54</v>
+        <v>13.96</v>
       </c>
       <c r="D31" s="66">
         <v>23.59</v>
@@ -1397,7 +1397,7 @@
         <v>12.57</v>
       </c>
       <c t="n" r="F31">
-        <v>287.1</v>
+        <v>268.3</v>
       </c>
       <c t="inlineStr" r="G31">
         <is>
@@ -1405,10 +1405,10 @@
         </is>
       </c>
       <c r="H31" s="66">
-        <v>0.55</v>
+        <v>0.51</v>
       </c>
       <c r="I31" s="65">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c t="inlineStr" r="J31">
         <is>
